--- a/Proyectos/Diseno-Estructural/DISENO-TODAS-LAS-VIGUETAS.xlsx
+++ b/Proyectos/Diseno-Estructural/DISENO-TODAS-LAS-VIGUETAS.xlsx
@@ -48,7 +48,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,56 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A2C4C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5A6BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B6D7A8"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,13 +162,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -142,7 +195,68 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -508,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD67"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -813,105 +927,105 @@
       <c r="B4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>1EC</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="11">
         <f>IF(C4="1EC",10,IF(C4="2EC",11,2))</f>
         <v>10</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="11">
         <f>IF(C4="1EC",14,IF(C4="2EC",16,0))</f>
         <v>14</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="12">
         <f>E4*D4^2/F4</f>
         <v>11.197264</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="12">
         <f>IF(C4="V",0,E4*D4^2/G4)</f>
         <v>7.998045714</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="12">
         <f>IF(C4="V",E4*D4,IF(C4="1EC",1.15,1)*E4*D4/2)</f>
         <v>19.810544</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="11">
         <f>MIN(D4*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="13">
         <f>I4*1000000/(0.9*K4*$Z$2^2)</f>
         <v>0.1204771859</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L4/(0.85*$B$2)))</f>
         <v>0.0002875801693</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="11">
         <f>M4*K4*$Z$2</f>
         <v>69.85897472</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="11">
         <f>MAX(N4,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="15">
         <f>ROUNDUP(O4/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="Q4" s="12">
         <f>O4*$D$2/(0.85*$B$2*K4)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R4" s="15" t="str">
+      <c r="R4" s="16" t="str">
         <f>IF(Q4&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S4" s="12">
+      <c r="S4" s="13">
         <f>H4*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.8995629881</v>
       </c>
-      <c r="T4" s="13">
+      <c r="T4" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S4/(0.85*$B$2)))</f>
         <v>0.002183899739</v>
       </c>
-      <c r="U4" s="10">
+      <c r="U4" s="11">
         <f>T4*$H$2*1000*$Z$2</f>
         <v>99.47117335</v>
       </c>
-      <c r="V4" s="10">
+      <c r="V4" s="11">
         <f>MAX(U4,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W4" s="14">
+      <c r="W4" s="15">
         <f>ROUNDUP(V4/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X4" s="15" t="str">
+      <c r="X4" s="16" t="str">
         <f>IF(J4&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y4" s="12">
+      <c r="Y4" s="13">
         <f>D4/IF(C4="1EC",18.5,IF(C4="2EC",21,8))</f>
         <v>0.1756756757</v>
       </c>
-      <c r="Z4" s="15" t="str">
+      <c r="Z4" s="16" t="str">
         <f>IF($J$2&gt;=Y4,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 1</t>
         </is>
@@ -919,105 +1033,105 @@
       <c r="B5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="11">
         <f>IF(C5="1EC",10,IF(C5="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="11">
         <f>IF(C5="1EC",14,IF(C5="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="12">
         <f>E5*D5^2/F5</f>
         <v>4.6644224</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="12">
         <f>IF(C5="V",0,E5*D5^2/G5)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="12">
         <f>IF(C5="V",E5*D5,IF(C5="1EC",1.15,1)*E5*D5/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="11">
         <f>MIN(D5*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="13">
         <f>I5*1000000/(0.9*K5*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L5/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="11">
         <f>M5*K5*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="11">
         <f>MAX(N5,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="15">
         <f>ROUNDUP(O5/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="12">
         <f>O5*$D$2/(0.85*$B$2*K5)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R5" s="15" t="str">
+      <c r="R5" s="16" t="str">
         <f>IF(Q5&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S5" s="12">
+      <c r="S5" s="13">
         <f>H5*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T5" s="13">
+      <c r="T5" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S5/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U5" s="10">
+      <c r="U5" s="11">
         <f>T5*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V5" s="10">
+      <c r="V5" s="11">
         <f>MAX(U5,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W5" s="14">
+      <c r="W5" s="15">
         <f>ROUNDUP(V5/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X5" s="15" t="str">
+      <c r="X5" s="16" t="str">
         <f>IF(J5&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y5" s="12">
+      <c r="Y5" s="13">
         <f>D5/IF(C5="1EC",18.5,IF(C5="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z5" s="15" t="str">
+      <c r="Z5" s="16" t="str">
         <f>IF($J$2&gt;=Y5,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 1</t>
         </is>
@@ -1025,105 +1139,105 @@
       <c r="B6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="11">
         <f>IF(C6="1EC",10,IF(C6="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="11">
         <f>IF(C6="1EC",14,IF(C6="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="12">
         <f>E6*D6^2/F6</f>
         <v>4.250021236</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="12">
         <f>IF(C6="V",0,E6*D6^2/G6)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="12">
         <f>IF(C6="V",E6*D6,IF(C6="1EC",1.15,1)*E6*D6/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="11">
         <f>MIN(D6*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="13">
         <f>I6*1000000/(0.9*K6*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L6/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="11">
         <f>M6*K6*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="11">
         <f>MAX(N6,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="15">
         <f>ROUNDUP(O6/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6" s="12">
         <f>O6*$D$2/(0.85*$B$2*K6)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R6" s="15" t="str">
+      <c r="R6" s="16" t="str">
         <f>IF(Q6&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="13">
         <f>H6*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T6" s="13">
+      <c r="T6" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S6/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U6" s="10">
+      <c r="U6" s="11">
         <f>T6*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V6" s="10">
+      <c r="V6" s="11">
         <f>MAX(U6,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W6" s="14">
+      <c r="W6" s="15">
         <f>ROUNDUP(V6/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X6" s="15" t="str">
+      <c r="X6" s="16" t="str">
         <f>IF(J6&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y6" s="12">
+      <c r="Y6" s="13">
         <f>D6/IF(C6="1EC",18.5,IF(C6="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z6" s="15" t="str">
+      <c r="Z6" s="16" t="str">
         <f>IF($J$2&gt;=Y6,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>VIGUETA 1</t>
         </is>
@@ -1131,105 +1245,105 @@
       <c r="B7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="22" t="n">
         <v>3.6</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="11">
         <f>IF(C7="1EC",10,IF(C7="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="11">
         <f>IF(C7="1EC",14,IF(C7="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="12">
         <f>E7*D7^2/F7</f>
         <v>12.48985833</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="12">
         <f>IF(C7="V",0,E7*D7^2/G7)</f>
         <v>8.5867776</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="12">
         <f>IF(C7="V",E7*D7,IF(C7="1EC",1.15,1)*E7*D7/2)</f>
         <v>19.081728</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="11">
         <f>MIN(D7*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="13">
         <f>I7*1000000/(0.9*K7*$Z$2^2)</f>
         <v>0.1293454474</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L7/(0.85*$B$2)))</f>
         <v>0.000308806777</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="11">
         <f>M7*K7*$Z$2</f>
         <v>75.01534228</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="11">
         <f>MAX(N7,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="15">
         <f>ROUNDUP(O7/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="Q7" s="12">
         <f>O7*$D$2/(0.85*$B$2*K7)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R7" s="15" t="str">
+      <c r="R7" s="16" t="str">
         <f>IF(Q7&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="13">
         <f>H7*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.003407107</v>
       </c>
-      <c r="T7" s="13">
+      <c r="T7" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S7/(0.85*$B$2)))</f>
         <v>0.002441668159</v>
       </c>
-      <c r="U7" s="10">
+      <c r="U7" s="11">
         <f>T7*$H$2*1000*$Z$2</f>
         <v>111.2118805</v>
       </c>
-      <c r="V7" s="10">
+      <c r="V7" s="11">
         <f>MAX(U7,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W7" s="14">
+      <c r="W7" s="15">
         <f>ROUNDUP(V7/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X7" s="15" t="str">
+      <c r="X7" s="16" t="str">
         <f>IF(J7&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y7" s="12">
+      <c r="Y7" s="13">
         <f>D7/IF(C7="1EC",18.5,IF(C7="2EC",21,8))</f>
         <v>0.1714285714</v>
       </c>
-      <c r="Z7" s="15" t="str">
+      <c r="Z7" s="16" t="str">
         <f>IF($J$2&gt;=Y7,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>VIGUETA 1</t>
         </is>
@@ -1237,105 +1351,105 @@
       <c r="B8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="24" t="n">
         <v>5.1</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <f>IF(C8="1EC",10,IF(C8="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="11">
         <f>IF(C8="1EC",14,IF(C8="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="12">
         <f>E8*D8^2/F8</f>
         <v>25.06645178</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="12">
         <f>IF(C8="V",0,E8*D8^2/G8)</f>
         <v>17.2331856</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="12">
         <f>IF(C8="V",E8*D8,IF(C8="1EC",1.15,1)*E8*D8/2)</f>
         <v>27.032448</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="11">
         <f>MIN(D8*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="13">
         <f>I8*1000000/(0.9*K8*$Z$2^2)</f>
         <v>0.2595891271</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L8/(0.85*$B$2)))</f>
         <v>0.0006214772975</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="11">
         <f>M8*K8*$Z$2</f>
         <v>150.9692651</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="11">
         <f>MAX(N8,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="15">
         <f>ROUNDUP(O8/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="Q8" s="12">
         <f>O8*$D$2/(0.85*$B$2*K8)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R8" s="15" t="str">
+      <c r="R8" s="16" t="str">
         <f>IF(Q8&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="13">
         <f>H8*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>2.013782319</v>
       </c>
-      <c r="T8" s="13">
+      <c r="T8" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S8/(0.85*$B$2)))</f>
         <v>0.005016792195</v>
       </c>
-      <c r="U8" s="10">
+      <c r="U8" s="11">
         <f>T8*$H$2*1000*$Z$2</f>
         <v>228.5023425</v>
       </c>
-      <c r="V8" s="10">
+      <c r="V8" s="11">
         <f>MAX(U8,$AB$2)</f>
         <v>228.5023425</v>
       </c>
-      <c r="W8" s="14">
+      <c r="W8" s="15">
         <f>ROUNDUP(V8/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X8" s="15" t="str">
+      <c r="X8" s="16" t="str">
         <f>IF(J8&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y8" s="12">
+      <c r="Y8" s="13">
         <f>D8/IF(C8="1EC",18.5,IF(C8="2EC",21,8))</f>
         <v>0.2428571429</v>
       </c>
-      <c r="Z8" s="15" t="str">
+      <c r="Z8" s="16" t="str">
         <f>IF($J$2&gt;=Y8,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>VIGUETA 1</t>
         </is>
@@ -1343,105 +1457,105 @@
       <c r="B9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="22" t="n">
         <v>3.6</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <f>IF(C9="1EC",10,IF(C9="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="11">
         <f>IF(C9="1EC",14,IF(C9="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="12">
         <f>E9*D9^2/F9</f>
         <v>12.48985833</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="12">
         <f>IF(C9="V",0,E9*D9^2/G9)</f>
         <v>8.5867776</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="12">
         <f>IF(C9="V",E9*D9,IF(C9="1EC",1.15,1)*E9*D9/2)</f>
         <v>19.081728</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="11">
         <f>MIN(D9*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="13">
         <f>I9*1000000/(0.9*K9*$Z$2^2)</f>
         <v>0.1293454474</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L9/(0.85*$B$2)))</f>
         <v>0.000308806777</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="11">
         <f>M9*K9*$Z$2</f>
         <v>75.01534228</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="11">
         <f>MAX(N9,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="15">
         <f>ROUNDUP(O9/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="Q9" s="12">
         <f>O9*$D$2/(0.85*$B$2*K9)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R9" s="15" t="str">
+      <c r="R9" s="16" t="str">
         <f>IF(Q9&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S9" s="12">
+      <c r="S9" s="13">
         <f>H9*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.003407107</v>
       </c>
-      <c r="T9" s="13">
+      <c r="T9" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S9/(0.85*$B$2)))</f>
         <v>0.002441668159</v>
       </c>
-      <c r="U9" s="10">
+      <c r="U9" s="11">
         <f>T9*$H$2*1000*$Z$2</f>
         <v>111.2118805</v>
       </c>
-      <c r="V9" s="10">
+      <c r="V9" s="11">
         <f>MAX(U9,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W9" s="14">
+      <c r="W9" s="15">
         <f>ROUNDUP(V9/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X9" s="15" t="str">
+      <c r="X9" s="16" t="str">
         <f>IF(J9&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y9" s="12">
+      <c r="Y9" s="13">
         <f>D9/IF(C9="1EC",18.5,IF(C9="2EC",21,8))</f>
         <v>0.1714285714</v>
       </c>
-      <c r="Z9" s="15" t="str">
+      <c r="Z9" s="16" t="str">
         <f>IF($J$2&gt;=Y9,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 1</t>
         </is>
@@ -1449,105 +1563,105 @@
       <c r="B10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="11">
         <f>IF(C10="1EC",10,IF(C10="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="11">
         <f>IF(C10="1EC",14,IF(C10="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="12">
         <f>E10*D10^2/F10</f>
         <v>4.250021236</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="12">
         <f>IF(C10="V",0,E10*D10^2/G10)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="12">
         <f>IF(C10="V",E10*D10,IF(C10="1EC",1.15,1)*E10*D10/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="11">
         <f>MIN(D10*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="13">
         <f>I10*1000000/(0.9*K10*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L10/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="11">
         <f>M10*K10*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="11">
         <f>MAX(N10,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P10" s="14">
+      <c r="P10" s="15">
         <f>ROUNDUP(O10/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q10" s="11">
+      <c r="Q10" s="12">
         <f>O10*$D$2/(0.85*$B$2*K10)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R10" s="15" t="str">
+      <c r="R10" s="16" t="str">
         <f>IF(Q10&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S10" s="12">
+      <c r="S10" s="13">
         <f>H10*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T10" s="13">
+      <c r="T10" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S10/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U10" s="10">
+      <c r="U10" s="11">
         <f>T10*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V10" s="10">
+      <c r="V10" s="11">
         <f>MAX(U10,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W10" s="14">
+      <c r="W10" s="15">
         <f>ROUNDUP(V10/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X10" s="15" t="str">
+      <c r="X10" s="16" t="str">
         <f>IF(J10&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y10" s="12">
+      <c r="Y10" s="13">
         <f>D10/IF(C10="1EC",18.5,IF(C10="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z10" s="15" t="str">
+      <c r="Z10" s="16" t="str">
         <f>IF($J$2&gt;=Y10,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 1</t>
         </is>
@@ -1555,99 +1669,99 @@
       <c r="B11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <f>IF(C11="1EC",10,IF(C11="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="11">
         <f>IF(C11="1EC",14,IF(C11="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="12">
         <f>E11*D11^2/F11</f>
         <v>4.6644224</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="12">
         <f>IF(C11="V",0,E11*D11^2/G11)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="12">
         <f>IF(C11="V",E11*D11,IF(C11="1EC",1.15,1)*E11*D11/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="11">
         <f>MIN(D11*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="13">
         <f>I11*1000000/(0.9*K11*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L11/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="11">
         <f>M11*K11*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="11">
         <f>MAX(N11,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P11" s="14">
+      <c r="P11" s="15">
         <f>ROUNDUP(O11/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q11" s="11">
+      <c r="Q11" s="12">
         <f>O11*$D$2/(0.85*$B$2*K11)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R11" s="15" t="str">
+      <c r="R11" s="16" t="str">
         <f>IF(Q11&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S11" s="12">
+      <c r="S11" s="13">
         <f>H11*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T11" s="13">
+      <c r="T11" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S11/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U11" s="10">
+      <c r="U11" s="11">
         <f>T11*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V11" s="10">
+      <c r="V11" s="11">
         <f>MAX(U11,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W11" s="14">
+      <c r="W11" s="15">
         <f>ROUNDUP(V11/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X11" s="15" t="str">
+      <c r="X11" s="16" t="str">
         <f>IF(J11&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y11" s="12">
+      <c r="Y11" s="13">
         <f>D11/IF(C11="1EC",18.5,IF(C11="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z11" s="15" t="str">
+      <c r="Z11" s="16" t="str">
         <f>IF($J$2&gt;=Y11,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
@@ -1661,105 +1775,105 @@
       <c r="B12" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>1EC</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="11">
         <f>IF(C12="1EC",10,IF(C12="2EC",11,2))</f>
         <v>10</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="11">
         <f>IF(C12="1EC",14,IF(C12="2EC",16,0))</f>
         <v>14</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="12">
         <f>E12*D12^2/F12</f>
         <v>11.197264</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="12">
         <f>IF(C12="V",0,E12*D12^2/G12)</f>
         <v>7.998045714</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="12">
         <f>IF(C12="V",E12*D12,IF(C12="1EC",1.15,1)*E12*D12/2)</f>
         <v>19.810544</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="11">
         <f>MIN(D12*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="13">
         <f>I12*1000000/(0.9*K12*$Z$2^2)</f>
         <v>0.1204771859</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L12/(0.85*$B$2)))</f>
         <v>0.0002875801693</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="11">
         <f>M12*K12*$Z$2</f>
         <v>69.85897472</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="11">
         <f>MAX(N12,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P12" s="14">
+      <c r="P12" s="15">
         <f>ROUNDUP(O12/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="Q12" s="12">
         <f>O12*$D$2/(0.85*$B$2*K12)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R12" s="15" t="str">
+      <c r="R12" s="16" t="str">
         <f>IF(Q12&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S12" s="12">
+      <c r="S12" s="13">
         <f>H12*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.8995629881</v>
       </c>
-      <c r="T12" s="13">
+      <c r="T12" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S12/(0.85*$B$2)))</f>
         <v>0.002183899739</v>
       </c>
-      <c r="U12" s="10">
+      <c r="U12" s="11">
         <f>T12*$H$2*1000*$Z$2</f>
         <v>99.47117335</v>
       </c>
-      <c r="V12" s="10">
+      <c r="V12" s="11">
         <f>MAX(U12,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W12" s="14">
+      <c r="W12" s="15">
         <f>ROUNDUP(V12/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X12" s="15" t="str">
+      <c r="X12" s="16" t="str">
         <f>IF(J12&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y12" s="12">
+      <c r="Y12" s="13">
         <f>D12/IF(C12="1EC",18.5,IF(C12="2EC",21,8))</f>
         <v>0.1756756757</v>
       </c>
-      <c r="Z12" s="15" t="str">
+      <c r="Z12" s="16" t="str">
         <f>IF($J$2&gt;=Y12,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 2</t>
         </is>
@@ -1767,99 +1881,99 @@
       <c r="B13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>1EC</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="11">
         <f>IF(C13="1EC",10,IF(C13="2EC",11,2))</f>
         <v>10</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="11">
         <f>IF(C13="1EC",14,IF(C13="2EC",16,0))</f>
         <v>14</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="12">
         <f>E13*D13^2/F13</f>
         <v>5.13086464</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="12">
         <f>IF(C13="V",0,E13*D13^2/G13)</f>
         <v>3.664903314</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="12">
         <f>IF(C13="V",E13*D13,IF(C13="1EC",1.15,1)*E13*D13/2)</f>
         <v>13.4102144</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="11">
         <f>MIN(D13*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="13">
         <f>I13*1000000/(0.9*K13*$Z$2^2)</f>
         <v>0.08029911373</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L13/(0.85*$B$2)))</f>
         <v>0.0001915119852</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="11">
         <f>M13*K13*$Z$2</f>
         <v>31.98393787</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="11">
         <f>MAX(N13,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P13" s="14">
+      <c r="P13" s="15">
         <f>ROUNDUP(O13/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="12">
         <f>O13*$D$2/(0.85*$B$2*K13)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R13" s="15" t="str">
+      <c r="R13" s="16" t="str">
         <f>IF(Q13&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S13" s="12">
+      <c r="S13" s="13">
         <f>H13*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.4122021171</v>
       </c>
-      <c r="T13" s="13">
+      <c r="T13" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S13/(0.85*$B$2)))</f>
         <v>0.0009900830036</v>
       </c>
-      <c r="U13" s="10">
+      <c r="U13" s="11">
         <f>T13*$H$2*1000*$Z$2</f>
         <v>45.09580561</v>
       </c>
-      <c r="V13" s="10">
+      <c r="V13" s="11">
         <f>MAX(U13,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W13" s="14">
+      <c r="W13" s="15">
         <f>ROUNDUP(V13/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X13" s="15" t="str">
+      <c r="X13" s="16" t="str">
         <f>IF(J13&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y13" s="12">
+      <c r="Y13" s="13">
         <f>D13/IF(C13="1EC",18.5,IF(C13="2EC",21,8))</f>
         <v>0.1189189189</v>
       </c>
-      <c r="Z13" s="15" t="str">
+      <c r="Z13" s="16" t="str">
         <f>IF($J$2&gt;=Y13,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
@@ -1873,105 +1987,105 @@
       <c r="B14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="11">
         <f>IF(C14="1EC",10,IF(C14="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="11">
         <f>IF(C14="1EC",14,IF(C14="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="12">
         <f>E14*D14^2/F14</f>
         <v>10.17933091</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="12">
         <f>IF(C14="V",0,E14*D14^2/G14)</f>
         <v>6.99829</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="12">
         <f>IF(C14="V",E14*D14,IF(C14="1EC",1.15,1)*E14*D14/2)</f>
         <v>17.22656</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="11">
         <f>MIN(D14*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="13">
         <f>I14*1000000/(0.9*K14*$Z$2^2)</f>
         <v>0.1054175377</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L14/(0.85*$B$2)))</f>
         <v>0.0002515524783</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="11">
         <f>M14*K14*$Z$2</f>
         <v>61.10712803</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="11">
         <f>MAX(N14,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P14" s="14">
+      <c r="P14" s="15">
         <f>ROUNDUP(O14/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="Q14" s="12">
         <f>O14*$D$2/(0.85*$B$2*K14)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R14" s="15" t="str">
+      <c r="R14" s="16" t="str">
         <f>IF(Q14&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S14" s="12">
+      <c r="S14" s="13">
         <f>H14*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.8177845346</v>
       </c>
-      <c r="T14" s="13">
+      <c r="T14" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S14/(0.85*$B$2)))</f>
         <v>0.001981759299</v>
       </c>
-      <c r="U14" s="10">
+      <c r="U14" s="11">
         <f>T14*$H$2*1000*$Z$2</f>
         <v>90.26418166</v>
       </c>
-      <c r="V14" s="10">
+      <c r="V14" s="11">
         <f>MAX(U14,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W14" s="14">
+      <c r="W14" s="15">
         <f>ROUNDUP(V14/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X14" s="15" t="str">
+      <c r="X14" s="16" t="str">
         <f>IF(J14&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y14" s="12">
+      <c r="Y14" s="13">
         <f>D14/IF(C14="1EC",18.5,IF(C14="2EC",21,8))</f>
         <v>0.1547619048</v>
       </c>
-      <c r="Z14" s="15" t="str">
+      <c r="Z14" s="16" t="str">
         <f>IF($J$2&gt;=Y14,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 2</t>
         </is>
@@ -1979,105 +2093,105 @@
       <c r="B15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="11">
         <f>IF(C15="1EC",10,IF(C15="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="11">
         <f>IF(C15="1EC",14,IF(C15="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="12">
         <f>E15*D15^2/F15</f>
         <v>4.6644224</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="12">
         <f>IF(C15="V",0,E15*D15^2/G15)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="12">
         <f>IF(C15="V",E15*D15,IF(C15="1EC",1.15,1)*E15*D15/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="11">
         <f>MIN(D15*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="13">
         <f>I15*1000000/(0.9*K15*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L15/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="11">
         <f>M15*K15*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="11">
         <f>MAX(N15,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P15" s="14">
+      <c r="P15" s="15">
         <f>ROUNDUP(O15/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q15" s="11">
+      <c r="Q15" s="12">
         <f>O15*$D$2/(0.85*$B$2*K15)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R15" s="15" t="str">
+      <c r="R15" s="16" t="str">
         <f>IF(Q15&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S15" s="12">
+      <c r="S15" s="13">
         <f>H15*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T15" s="13">
+      <c r="T15" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S15/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U15" s="10">
+      <c r="U15" s="11">
         <f>T15*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V15" s="10">
+      <c r="V15" s="11">
         <f>MAX(U15,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W15" s="14">
+      <c r="W15" s="15">
         <f>ROUNDUP(V15/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X15" s="15" t="str">
+      <c r="X15" s="16" t="str">
         <f>IF(J15&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y15" s="12">
+      <c r="Y15" s="13">
         <f>D15/IF(C15="1EC",18.5,IF(C15="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z15" s="15" t="str">
+      <c r="Z15" s="16" t="str">
         <f>IF($J$2&gt;=Y15,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 2</t>
         </is>
@@ -2085,105 +2199,105 @@
       <c r="B16" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="11">
         <f>IF(C16="1EC",10,IF(C16="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="11">
         <f>IF(C16="1EC",14,IF(C16="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="12">
         <f>E16*D16^2/F16</f>
         <v>4.250021236</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="12">
         <f>IF(C16="V",0,E16*D16^2/G16)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="12">
         <f>IF(C16="V",E16*D16,IF(C16="1EC",1.15,1)*E16*D16/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="11">
         <f>MIN(D16*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="13">
         <f>I16*1000000/(0.9*K16*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L16/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="11">
         <f>M16*K16*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O16" s="10">
+      <c r="O16" s="11">
         <f>MAX(N16,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P16" s="14">
+      <c r="P16" s="15">
         <f>ROUNDUP(O16/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q16" s="11">
+      <c r="Q16" s="12">
         <f>O16*$D$2/(0.85*$B$2*K16)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R16" s="15" t="str">
+      <c r="R16" s="16" t="str">
         <f>IF(Q16&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S16" s="12">
+      <c r="S16" s="13">
         <f>H16*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T16" s="13">
+      <c r="T16" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S16/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U16" s="10">
+      <c r="U16" s="11">
         <f>T16*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V16" s="10">
+      <c r="V16" s="11">
         <f>MAX(U16,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W16" s="14">
+      <c r="W16" s="15">
         <f>ROUNDUP(V16/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X16" s="15" t="str">
+      <c r="X16" s="16" t="str">
         <f>IF(J16&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y16" s="12">
+      <c r="Y16" s="13">
         <f>D16/IF(C16="1EC",18.5,IF(C16="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z16" s="15" t="str">
+      <c r="Z16" s="16" t="str">
         <f>IF($J$2&gt;=Y16,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>VIGUETA 2</t>
         </is>
@@ -2191,105 +2305,105 @@
       <c r="B17" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="22" t="n">
         <v>3.6</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="11">
         <f>IF(C17="1EC",10,IF(C17="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="11">
         <f>IF(C17="1EC",14,IF(C17="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="12">
         <f>E17*D17^2/F17</f>
         <v>12.48985833</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="12">
         <f>IF(C17="V",0,E17*D17^2/G17)</f>
         <v>8.5867776</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="12">
         <f>IF(C17="V",E17*D17,IF(C17="1EC",1.15,1)*E17*D17/2)</f>
         <v>19.081728</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="11">
         <f>MIN(D17*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="13">
         <f>I17*1000000/(0.9*K17*$Z$2^2)</f>
         <v>0.1293454474</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L17/(0.85*$B$2)))</f>
         <v>0.000308806777</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="11">
         <f>M17*K17*$Z$2</f>
         <v>75.01534228</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="11">
         <f>MAX(N17,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P17" s="14">
+      <c r="P17" s="15">
         <f>ROUNDUP(O17/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q17" s="11">
+      <c r="Q17" s="12">
         <f>O17*$D$2/(0.85*$B$2*K17)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R17" s="15" t="str">
+      <c r="R17" s="16" t="str">
         <f>IF(Q17&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S17" s="12">
+      <c r="S17" s="13">
         <f>H17*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.003407107</v>
       </c>
-      <c r="T17" s="13">
+      <c r="T17" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S17/(0.85*$B$2)))</f>
         <v>0.002441668159</v>
       </c>
-      <c r="U17" s="10">
+      <c r="U17" s="11">
         <f>T17*$H$2*1000*$Z$2</f>
         <v>111.2118805</v>
       </c>
-      <c r="V17" s="10">
+      <c r="V17" s="11">
         <f>MAX(U17,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W17" s="14">
+      <c r="W17" s="15">
         <f>ROUNDUP(V17/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X17" s="15" t="str">
+      <c r="X17" s="16" t="str">
         <f>IF(J17&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y17" s="12">
+      <c r="Y17" s="13">
         <f>D17/IF(C17="1EC",18.5,IF(C17="2EC",21,8))</f>
         <v>0.1714285714</v>
       </c>
-      <c r="Z17" s="15" t="str">
+      <c r="Z17" s="16" t="str">
         <f>IF($J$2&gt;=Y17,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>VIGUETA 2</t>
         </is>
@@ -2297,105 +2411,105 @@
       <c r="B18" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="24" t="n">
         <v>5.1</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="11">
         <f>IF(C18="1EC",10,IF(C18="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="11">
         <f>IF(C18="1EC",14,IF(C18="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="12">
         <f>E18*D18^2/F18</f>
         <v>25.06645178</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="12">
         <f>IF(C18="V",0,E18*D18^2/G18)</f>
         <v>17.2331856</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="12">
         <f>IF(C18="V",E18*D18,IF(C18="1EC",1.15,1)*E18*D18/2)</f>
         <v>27.032448</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="11">
         <f>MIN(D18*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="13">
         <f>I18*1000000/(0.9*K18*$Z$2^2)</f>
         <v>0.2595891271</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L18/(0.85*$B$2)))</f>
         <v>0.0006214772975</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="11">
         <f>M18*K18*$Z$2</f>
         <v>150.9692651</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="11">
         <f>MAX(N18,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P18" s="14">
+      <c r="P18" s="15">
         <f>ROUNDUP(O18/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q18" s="11">
+      <c r="Q18" s="12">
         <f>O18*$D$2/(0.85*$B$2*K18)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R18" s="15" t="str">
+      <c r="R18" s="16" t="str">
         <f>IF(Q18&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S18" s="12">
+      <c r="S18" s="13">
         <f>H18*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>2.013782319</v>
       </c>
-      <c r="T18" s="13">
+      <c r="T18" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S18/(0.85*$B$2)))</f>
         <v>0.005016792195</v>
       </c>
-      <c r="U18" s="10">
+      <c r="U18" s="11">
         <f>T18*$H$2*1000*$Z$2</f>
         <v>228.5023425</v>
       </c>
-      <c r="V18" s="10">
+      <c r="V18" s="11">
         <f>MAX(U18,$AB$2)</f>
         <v>228.5023425</v>
       </c>
-      <c r="W18" s="14">
+      <c r="W18" s="15">
         <f>ROUNDUP(V18/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X18" s="15" t="str">
+      <c r="X18" s="16" t="str">
         <f>IF(J18&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y18" s="12">
+      <c r="Y18" s="13">
         <f>D18/IF(C18="1EC",18.5,IF(C18="2EC",21,8))</f>
         <v>0.2428571429</v>
       </c>
-      <c r="Z18" s="15" t="str">
+      <c r="Z18" s="16" t="str">
         <f>IF($J$2&gt;=Y18,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>VIGUETA 2</t>
         </is>
@@ -2403,105 +2517,105 @@
       <c r="B19" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="22" t="n">
         <v>3.6</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="11">
         <f>IF(C19="1EC",10,IF(C19="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="11">
         <f>IF(C19="1EC",14,IF(C19="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="12">
         <f>E19*D19^2/F19</f>
         <v>12.48985833</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="12">
         <f>IF(C19="V",0,E19*D19^2/G19)</f>
         <v>8.5867776</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="12">
         <f>IF(C19="V",E19*D19,IF(C19="1EC",1.15,1)*E19*D19/2)</f>
         <v>19.081728</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="11">
         <f>MIN(D19*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="13">
         <f>I19*1000000/(0.9*K19*$Z$2^2)</f>
         <v>0.1293454474</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L19/(0.85*$B$2)))</f>
         <v>0.000308806777</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="11">
         <f>M19*K19*$Z$2</f>
         <v>75.01534228</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="11">
         <f>MAX(N19,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P19" s="14">
+      <c r="P19" s="15">
         <f>ROUNDUP(O19/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q19" s="11">
+      <c r="Q19" s="12">
         <f>O19*$D$2/(0.85*$B$2*K19)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R19" s="15" t="str">
+      <c r="R19" s="16" t="str">
         <f>IF(Q19&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S19" s="12">
+      <c r="S19" s="13">
         <f>H19*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.003407107</v>
       </c>
-      <c r="T19" s="13">
+      <c r="T19" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S19/(0.85*$B$2)))</f>
         <v>0.002441668159</v>
       </c>
-      <c r="U19" s="10">
+      <c r="U19" s="11">
         <f>T19*$H$2*1000*$Z$2</f>
         <v>111.2118805</v>
       </c>
-      <c r="V19" s="10">
+      <c r="V19" s="11">
         <f>MAX(U19,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W19" s="14">
+      <c r="W19" s="15">
         <f>ROUNDUP(V19/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X19" s="15" t="str">
+      <c r="X19" s="16" t="str">
         <f>IF(J19&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y19" s="12">
+      <c r="Y19" s="13">
         <f>D19/IF(C19="1EC",18.5,IF(C19="2EC",21,8))</f>
         <v>0.1714285714</v>
       </c>
-      <c r="Z19" s="15" t="str">
+      <c r="Z19" s="16" t="str">
         <f>IF($J$2&gt;=Y19,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 2</t>
         </is>
@@ -2509,105 +2623,105 @@
       <c r="B20" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="11">
         <f>IF(C20="1EC",10,IF(C20="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="11">
         <f>IF(C20="1EC",14,IF(C20="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="12">
         <f>E20*D20^2/F20</f>
         <v>4.250021236</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="12">
         <f>IF(C20="V",0,E20*D20^2/G20)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="12">
         <f>IF(C20="V",E20*D20,IF(C20="1EC",1.15,1)*E20*D20/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="11">
         <f>MIN(D20*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="13">
         <f>I20*1000000/(0.9*K20*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M20" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L20/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="11">
         <f>M20*K20*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="11">
         <f>MAX(N20,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P20" s="14">
+      <c r="P20" s="15">
         <f>ROUNDUP(O20/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q20" s="11">
+      <c r="Q20" s="12">
         <f>O20*$D$2/(0.85*$B$2*K20)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R20" s="15" t="str">
+      <c r="R20" s="16" t="str">
         <f>IF(Q20&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S20" s="12">
+      <c r="S20" s="13">
         <f>H20*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T20" s="13">
+      <c r="T20" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S20/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U20" s="10">
+      <c r="U20" s="11">
         <f>T20*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V20" s="10">
+      <c r="V20" s="11">
         <f>MAX(U20,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W20" s="14">
+      <c r="W20" s="15">
         <f>ROUNDUP(V20/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X20" s="15" t="str">
+      <c r="X20" s="16" t="str">
         <f>IF(J20&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y20" s="12">
+      <c r="Y20" s="13">
         <f>D20/IF(C20="1EC",18.5,IF(C20="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z20" s="15" t="str">
+      <c r="Z20" s="16" t="str">
         <f>IF($J$2&gt;=Y20,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 2</t>
         </is>
@@ -2615,99 +2729,99 @@
       <c r="B21" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="11">
         <f>IF(C21="1EC",10,IF(C21="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="11">
         <f>IF(C21="1EC",14,IF(C21="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="12">
         <f>E21*D21^2/F21</f>
         <v>4.6644224</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="12">
         <f>IF(C21="V",0,E21*D21^2/G21)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="12">
         <f>IF(C21="V",E21*D21,IF(C21="1EC",1.15,1)*E21*D21/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="11">
         <f>MIN(D21*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="13">
         <f>I21*1000000/(0.9*K21*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L21/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="11">
         <f>M21*K21*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="11">
         <f>MAX(N21,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P21" s="14">
+      <c r="P21" s="15">
         <f>ROUNDUP(O21/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="Q21" s="12">
         <f>O21*$D$2/(0.85*$B$2*K21)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R21" s="15" t="str">
+      <c r="R21" s="16" t="str">
         <f>IF(Q21&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S21" s="12">
+      <c r="S21" s="13">
         <f>H21*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T21" s="13">
+      <c r="T21" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S21/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U21" s="10">
+      <c r="U21" s="11">
         <f>T21*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V21" s="10">
+      <c r="V21" s="11">
         <f>MAX(U21,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W21" s="14">
+      <c r="W21" s="15">
         <f>ROUNDUP(V21/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X21" s="15" t="str">
+      <c r="X21" s="16" t="str">
         <f>IF(J21&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y21" s="12">
+      <c r="Y21" s="13">
         <f>D21/IF(C21="1EC",18.5,IF(C21="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z21" s="15" t="str">
+      <c r="Z21" s="16" t="str">
         <f>IF($J$2&gt;=Y21,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
@@ -2721,105 +2835,105 @@
       <c r="B22" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="11">
         <f>IF(C22="1EC",10,IF(C22="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="11">
         <f>IF(C22="1EC",14,IF(C22="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="12">
         <f>E22*D22^2/F22</f>
         <v>10.17933091</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="12">
         <f>IF(C22="V",0,E22*D22^2/G22)</f>
         <v>6.99829</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="12">
         <f>IF(C22="V",E22*D22,IF(C22="1EC",1.15,1)*E22*D22/2)</f>
         <v>17.22656</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="11">
         <f>MIN(D22*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="13">
         <f>I22*1000000/(0.9*K22*$Z$2^2)</f>
         <v>0.1054175377</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L22/(0.85*$B$2)))</f>
         <v>0.0002515524783</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="11">
         <f>M22*K22*$Z$2</f>
         <v>61.10712803</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="11">
         <f>MAX(N22,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P22" s="14">
+      <c r="P22" s="15">
         <f>ROUNDUP(O22/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q22" s="11">
+      <c r="Q22" s="12">
         <f>O22*$D$2/(0.85*$B$2*K22)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R22" s="15" t="str">
+      <c r="R22" s="16" t="str">
         <f>IF(Q22&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S22" s="12">
+      <c r="S22" s="13">
         <f>H22*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.8177845346</v>
       </c>
-      <c r="T22" s="13">
+      <c r="T22" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S22/(0.85*$B$2)))</f>
         <v>0.001981759299</v>
       </c>
-      <c r="U22" s="10">
+      <c r="U22" s="11">
         <f>T22*$H$2*1000*$Z$2</f>
         <v>90.26418166</v>
       </c>
-      <c r="V22" s="10">
+      <c r="V22" s="11">
         <f>MAX(U22,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W22" s="14">
+      <c r="W22" s="15">
         <f>ROUNDUP(V22/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X22" s="15" t="str">
+      <c r="X22" s="16" t="str">
         <f>IF(J22&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y22" s="12">
+      <c r="Y22" s="13">
         <f>D22/IF(C22="1EC",18.5,IF(C22="2EC",21,8))</f>
         <v>0.1547619048</v>
       </c>
-      <c r="Z22" s="15" t="str">
+      <c r="Z22" s="16" t="str">
         <f>IF($J$2&gt;=Y22,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 2</t>
         </is>
@@ -2827,105 +2941,105 @@
       <c r="B23" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>1EC</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="11">
         <f>IF(C23="1EC",10,IF(C23="2EC",11,2))</f>
         <v>10</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="11">
         <f>IF(C23="1EC",14,IF(C23="2EC",16,0))</f>
         <v>14</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="12">
         <f>E23*D23^2/F23</f>
         <v>5.13086464</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="12">
         <f>IF(C23="V",0,E23*D23^2/G23)</f>
         <v>3.664903314</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="12">
         <f>IF(C23="V",E23*D23,IF(C23="1EC",1.15,1)*E23*D23/2)</f>
         <v>13.4102144</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="11">
         <f>MIN(D23*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="13">
         <f>I23*1000000/(0.9*K23*$Z$2^2)</f>
         <v>0.08029911373</v>
       </c>
-      <c r="M23" s="13">
+      <c r="M23" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L23/(0.85*$B$2)))</f>
         <v>0.0001915119852</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="11">
         <f>M23*K23*$Z$2</f>
         <v>31.98393787</v>
       </c>
-      <c r="O23" s="10">
+      <c r="O23" s="11">
         <f>MAX(N23,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P23" s="14">
+      <c r="P23" s="15">
         <f>ROUNDUP(O23/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q23" s="11">
+      <c r="Q23" s="12">
         <f>O23*$D$2/(0.85*$B$2*K23)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R23" s="15" t="str">
+      <c r="R23" s="16" t="str">
         <f>IF(Q23&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S23" s="12">
+      <c r="S23" s="13">
         <f>H23*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.4122021171</v>
       </c>
-      <c r="T23" s="13">
+      <c r="T23" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S23/(0.85*$B$2)))</f>
         <v>0.0009900830036</v>
       </c>
-      <c r="U23" s="10">
+      <c r="U23" s="11">
         <f>T23*$H$2*1000*$Z$2</f>
         <v>45.09580561</v>
       </c>
-      <c r="V23" s="10">
+      <c r="V23" s="11">
         <f>MAX(U23,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W23" s="14">
+      <c r="W23" s="15">
         <f>ROUNDUP(V23/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X23" s="15" t="str">
+      <c r="X23" s="16" t="str">
         <f>IF(J23&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y23" s="12">
+      <c r="Y23" s="13">
         <f>D23/IF(C23="1EC",18.5,IF(C23="2EC",21,8))</f>
         <v>0.1189189189</v>
       </c>
-      <c r="Z23" s="15" t="str">
+      <c r="Z23" s="16" t="str">
         <f>IF($J$2&gt;=Y23,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -2933,105 +3047,105 @@
       <c r="B24" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="11">
         <f>IF(C24="1EC",10,IF(C24="2EC",11,2))</f>
         <v>2</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="11">
         <f>IF(C24="1EC",14,IF(C24="2EC",16,0))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="12">
         <f>E24*D24^2/F24</f>
         <v>11.92608</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="12">
         <f>IF(C24="V",0,E24*D24^2/G24)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="12">
         <f>IF(C24="V",E24*D24,IF(C24="1EC",1.15,1)*E24*D24/2)</f>
         <v>15.90144</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="11">
         <f>MIN(D24*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>375</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="13">
         <f>I24*1000000/(0.9*K24*$Z$2^2)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="13">
+      <c r="M24" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L24/(0.85*$B$2)))</f>
         <v>0</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="11">
         <f>M24*K24*$Z$2</f>
         <v>0</v>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="11">
         <f>MAX(N24,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P24" s="14">
+      <c r="P24" s="15">
         <f>ROUNDUP(O24/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q24" s="11">
+      <c r="Q24" s="12">
         <f>O24*$D$2/(0.85*$B$2*K24)</f>
         <v>7.144705882</v>
       </c>
-      <c r="R24" s="15" t="str">
+      <c r="R24" s="16" t="str">
         <f>IF(Q24&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S24" s="12">
+      <c r="S24" s="13">
         <f>H24*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.9581144251</v>
       </c>
-      <c r="T24" s="13">
+      <c r="T24" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S24/(0.85*$B$2)))</f>
         <v>0.002329089448</v>
       </c>
-      <c r="U24" s="10">
+      <c r="U24" s="11">
         <f>T24*$H$2*1000*$Z$2</f>
         <v>106.0842016</v>
       </c>
-      <c r="V24" s="10">
+      <c r="V24" s="11">
         <f>MAX(U24,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W24" s="14">
+      <c r="W24" s="15">
         <f>ROUNDUP(V24/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X24" s="15" t="str">
+      <c r="X24" s="16" t="str">
         <f>IF(J24&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y24" s="12">
+      <c r="Y24" s="13">
         <f>D24/IF(C24="1EC",18.5,IF(C24="2EC",21,8))</f>
         <v>0.1875</v>
       </c>
-      <c r="Z24" s="15" t="str">
+      <c r="Z24" s="16" t="str">
         <f>IF($J$2&gt;=Y24,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -3039,99 +3153,99 @@
       <c r="B25" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="11">
         <f>IF(C25="1EC",10,IF(C25="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="11">
         <f>IF(C25="1EC",14,IF(C25="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="12">
         <f>E25*D25^2/F25</f>
         <v>4.6644224</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="12">
         <f>IF(C25="V",0,E25*D25^2/G25)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="12">
         <f>IF(C25="V",E25*D25,IF(C25="1EC",1.15,1)*E25*D25/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="11">
         <f>MIN(D25*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="13">
         <f>I25*1000000/(0.9*K25*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M25" s="13">
+      <c r="M25" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L25/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N25" s="11">
         <f>M25*K25*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O25" s="10">
+      <c r="O25" s="11">
         <f>MAX(N25,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P25" s="14">
+      <c r="P25" s="15">
         <f>ROUNDUP(O25/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q25" s="11">
+      <c r="Q25" s="12">
         <f>O25*$D$2/(0.85*$B$2*K25)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R25" s="15" t="str">
+      <c r="R25" s="16" t="str">
         <f>IF(Q25&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S25" s="12">
+      <c r="S25" s="13">
         <f>H25*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T25" s="13">
+      <c r="T25" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S25/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U25" s="10">
+      <c r="U25" s="11">
         <f>T25*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V25" s="10">
+      <c r="V25" s="11">
         <f>MAX(U25,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W25" s="14">
+      <c r="W25" s="15">
         <f>ROUNDUP(V25/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X25" s="15" t="str">
+      <c r="X25" s="16" t="str">
         <f>IF(J25&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y25" s="12">
+      <c r="Y25" s="13">
         <f>D25/IF(C25="1EC",18.5,IF(C25="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z25" s="15" t="str">
+      <c r="Z25" s="16" t="str">
         <f>IF($J$2&gt;=Y25,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
@@ -3145,105 +3259,105 @@
       <c r="B26" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="11">
         <f>IF(C26="1EC",10,IF(C26="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="11">
         <f>IF(C26="1EC",14,IF(C26="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="12">
         <f>E26*D26^2/F26</f>
         <v>10.17933091</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="12">
         <f>IF(C26="V",0,E26*D26^2/G26)</f>
         <v>6.99829</v>
       </c>
-      <c r="J26" s="11">
+      <c r="J26" s="12">
         <f>IF(C26="V",E26*D26,IF(C26="1EC",1.15,1)*E26*D26/2)</f>
         <v>17.22656</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="11">
         <f>MIN(D26*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="13">
         <f>I26*1000000/(0.9*K26*$Z$2^2)</f>
         <v>0.1054175377</v>
       </c>
-      <c r="M26" s="13">
+      <c r="M26" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L26/(0.85*$B$2)))</f>
         <v>0.0002515524783</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="11">
         <f>M26*K26*$Z$2</f>
         <v>61.10712803</v>
       </c>
-      <c r="O26" s="10">
+      <c r="O26" s="11">
         <f>MAX(N26,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P26" s="14">
+      <c r="P26" s="15">
         <f>ROUNDUP(O26/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q26" s="11">
+      <c r="Q26" s="12">
         <f>O26*$D$2/(0.85*$B$2*K26)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R26" s="15" t="str">
+      <c r="R26" s="16" t="str">
         <f>IF(Q26&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S26" s="12">
+      <c r="S26" s="13">
         <f>H26*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.8177845346</v>
       </c>
-      <c r="T26" s="13">
+      <c r="T26" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S26/(0.85*$B$2)))</f>
         <v>0.001981759299</v>
       </c>
-      <c r="U26" s="10">
+      <c r="U26" s="11">
         <f>T26*$H$2*1000*$Z$2</f>
         <v>90.26418166</v>
       </c>
-      <c r="V26" s="10">
+      <c r="V26" s="11">
         <f>MAX(U26,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W26" s="14">
+      <c r="W26" s="15">
         <f>ROUNDUP(V26/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X26" s="15" t="str">
+      <c r="X26" s="16" t="str">
         <f>IF(J26&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y26" s="12">
+      <c r="Y26" s="13">
         <f>D26/IF(C26="1EC",18.5,IF(C26="2EC",21,8))</f>
         <v>0.1547619048</v>
       </c>
-      <c r="Z26" s="15" t="str">
+      <c r="Z26" s="16" t="str">
         <f>IF($J$2&gt;=Y26,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -3251,105 +3365,105 @@
       <c r="B27" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="11">
         <f>IF(C27="1EC",10,IF(C27="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="11">
         <f>IF(C27="1EC",14,IF(C27="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="12">
         <f>E27*D27^2/F27</f>
         <v>4.6644224</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="12">
         <f>IF(C27="V",0,E27*D27^2/G27)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J27" s="11">
+      <c r="J27" s="12">
         <f>IF(C27="V",E27*D27,IF(C27="1EC",1.15,1)*E27*D27/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="11">
         <f>MIN(D27*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="13">
         <f>I27*1000000/(0.9*K27*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M27" s="13">
+      <c r="M27" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L27/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N27" s="11">
         <f>M27*K27*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O27" s="10">
+      <c r="O27" s="11">
         <f>MAX(N27,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P27" s="14">
+      <c r="P27" s="15">
         <f>ROUNDUP(O27/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q27" s="11">
+      <c r="Q27" s="12">
         <f>O27*$D$2/(0.85*$B$2*K27)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R27" s="15" t="str">
+      <c r="R27" s="16" t="str">
         <f>IF(Q27&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S27" s="12">
+      <c r="S27" s="13">
         <f>H27*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T27" s="13">
+      <c r="T27" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S27/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U27" s="10">
+      <c r="U27" s="11">
         <f>T27*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V27" s="10">
+      <c r="V27" s="11">
         <f>MAX(U27,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W27" s="14">
+      <c r="W27" s="15">
         <f>ROUNDUP(V27/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X27" s="15" t="str">
+      <c r="X27" s="16" t="str">
         <f>IF(J27&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y27" s="12">
+      <c r="Y27" s="13">
         <f>D27/IF(C27="1EC",18.5,IF(C27="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z27" s="15" t="str">
+      <c r="Z27" s="16" t="str">
         <f>IF($J$2&gt;=Y27,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -3357,105 +3471,105 @@
       <c r="B28" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="11">
         <f>IF(C28="1EC",10,IF(C28="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="11">
         <f>IF(C28="1EC",14,IF(C28="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="12">
         <f>E28*D28^2/F28</f>
         <v>4.250021236</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="12">
         <f>IF(C28="V",0,E28*D28^2/G28)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J28" s="11">
+      <c r="J28" s="12">
         <f>IF(C28="V",E28*D28,IF(C28="1EC",1.15,1)*E28*D28/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="11">
         <f>MIN(D28*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L28" s="12">
+      <c r="L28" s="13">
         <f>I28*1000000/(0.9*K28*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M28" s="13">
+      <c r="M28" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L28/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N28" s="10">
+      <c r="N28" s="11">
         <f>M28*K28*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O28" s="10">
+      <c r="O28" s="11">
         <f>MAX(N28,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P28" s="14">
+      <c r="P28" s="15">
         <f>ROUNDUP(O28/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q28" s="11">
+      <c r="Q28" s="12">
         <f>O28*$D$2/(0.85*$B$2*K28)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R28" s="15" t="str">
+      <c r="R28" s="16" t="str">
         <f>IF(Q28&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S28" s="12">
+      <c r="S28" s="13">
         <f>H28*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T28" s="13">
+      <c r="T28" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S28/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U28" s="10">
+      <c r="U28" s="11">
         <f>T28*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V28" s="10">
+      <c r="V28" s="11">
         <f>MAX(U28,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W28" s="14">
+      <c r="W28" s="15">
         <f>ROUNDUP(V28/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X28" s="15" t="str">
+      <c r="X28" s="16" t="str">
         <f>IF(J28&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y28" s="12">
+      <c r="Y28" s="13">
         <f>D28/IF(C28="1EC",18.5,IF(C28="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z28" s="15" t="str">
+      <c r="Z28" s="16" t="str">
         <f>IF($J$2&gt;=Y28,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -3463,105 +3577,105 @@
       <c r="B29" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="22" t="n">
         <v>3.6</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="11">
         <f>IF(C29="1EC",10,IF(C29="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="11">
         <f>IF(C29="1EC",14,IF(C29="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="12">
         <f>E29*D29^2/F29</f>
         <v>12.48985833</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="12">
         <f>IF(C29="V",0,E29*D29^2/G29)</f>
         <v>8.5867776</v>
       </c>
-      <c r="J29" s="11">
+      <c r="J29" s="12">
         <f>IF(C29="V",E29*D29,IF(C29="1EC",1.15,1)*E29*D29/2)</f>
         <v>19.081728</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="11">
         <f>MIN(D29*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="13">
         <f>I29*1000000/(0.9*K29*$Z$2^2)</f>
         <v>0.1293454474</v>
       </c>
-      <c r="M29" s="13">
+      <c r="M29" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L29/(0.85*$B$2)))</f>
         <v>0.000308806777</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N29" s="11">
         <f>M29*K29*$Z$2</f>
         <v>75.01534228</v>
       </c>
-      <c r="O29" s="10">
+      <c r="O29" s="11">
         <f>MAX(N29,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P29" s="14">
+      <c r="P29" s="15">
         <f>ROUNDUP(O29/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q29" s="11">
+      <c r="Q29" s="12">
         <f>O29*$D$2/(0.85*$B$2*K29)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R29" s="15" t="str">
+      <c r="R29" s="16" t="str">
         <f>IF(Q29&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S29" s="12">
+      <c r="S29" s="13">
         <f>H29*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.003407107</v>
       </c>
-      <c r="T29" s="13">
+      <c r="T29" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S29/(0.85*$B$2)))</f>
         <v>0.002441668159</v>
       </c>
-      <c r="U29" s="10">
+      <c r="U29" s="11">
         <f>T29*$H$2*1000*$Z$2</f>
         <v>111.2118805</v>
       </c>
-      <c r="V29" s="10">
+      <c r="V29" s="11">
         <f>MAX(U29,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W29" s="14">
+      <c r="W29" s="15">
         <f>ROUNDUP(V29/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X29" s="15" t="str">
+      <c r="X29" s="16" t="str">
         <f>IF(J29&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y29" s="12">
+      <c r="Y29" s="13">
         <f>D29/IF(C29="1EC",18.5,IF(C29="2EC",21,8))</f>
         <v>0.1714285714</v>
       </c>
-      <c r="Z29" s="15" t="str">
+      <c r="Z29" s="16" t="str">
         <f>IF($J$2&gt;=Y29,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -3569,105 +3683,105 @@
       <c r="B30" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="24" t="n">
         <v>5.1</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="11">
         <f>IF(C30="1EC",10,IF(C30="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="11">
         <f>IF(C30="1EC",14,IF(C30="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="12">
         <f>E30*D30^2/F30</f>
         <v>25.06645178</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="12">
         <f>IF(C30="V",0,E30*D30^2/G30)</f>
         <v>17.2331856</v>
       </c>
-      <c r="J30" s="11">
+      <c r="J30" s="12">
         <f>IF(C30="V",E30*D30,IF(C30="1EC",1.15,1)*E30*D30/2)</f>
         <v>27.032448</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="11">
         <f>MIN(D30*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L30" s="12">
+      <c r="L30" s="13">
         <f>I30*1000000/(0.9*K30*$Z$2^2)</f>
         <v>0.2595891271</v>
       </c>
-      <c r="M30" s="13">
+      <c r="M30" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L30/(0.85*$B$2)))</f>
         <v>0.0006214772975</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="11">
         <f>M30*K30*$Z$2</f>
         <v>150.9692651</v>
       </c>
-      <c r="O30" s="10">
+      <c r="O30" s="11">
         <f>MAX(N30,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P30" s="14">
+      <c r="P30" s="15">
         <f>ROUNDUP(O30/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q30" s="11">
+      <c r="Q30" s="12">
         <f>O30*$D$2/(0.85*$B$2*K30)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R30" s="15" t="str">
+      <c r="R30" s="16" t="str">
         <f>IF(Q30&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S30" s="12">
+      <c r="S30" s="13">
         <f>H30*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>2.013782319</v>
       </c>
-      <c r="T30" s="13">
+      <c r="T30" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S30/(0.85*$B$2)))</f>
         <v>0.005016792195</v>
       </c>
-      <c r="U30" s="10">
+      <c r="U30" s="11">
         <f>T30*$H$2*1000*$Z$2</f>
         <v>228.5023425</v>
       </c>
-      <c r="V30" s="10">
+      <c r="V30" s="11">
         <f>MAX(U30,$AB$2)</f>
         <v>228.5023425</v>
       </c>
-      <c r="W30" s="14">
+      <c r="W30" s="15">
         <f>ROUNDUP(V30/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X30" s="15" t="str">
+      <c r="X30" s="16" t="str">
         <f>IF(J30&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y30" s="12">
+      <c r="Y30" s="13">
         <f>D30/IF(C30="1EC",18.5,IF(C30="2EC",21,8))</f>
         <v>0.2428571429</v>
       </c>
-      <c r="Z30" s="15" t="str">
+      <c r="Z30" s="16" t="str">
         <f>IF($J$2&gt;=Y30,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -3675,105 +3789,105 @@
       <c r="B31" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="22" t="n">
         <v>3.6</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="11">
         <f>IF(C31="1EC",10,IF(C31="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="11">
         <f>IF(C31="1EC",14,IF(C31="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="12">
         <f>E31*D31^2/F31</f>
         <v>12.48985833</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="12">
         <f>IF(C31="V",0,E31*D31^2/G31)</f>
         <v>8.5867776</v>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="12">
         <f>IF(C31="V",E31*D31,IF(C31="1EC",1.15,1)*E31*D31/2)</f>
         <v>19.081728</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="11">
         <f>MIN(D31*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L31" s="12">
+      <c r="L31" s="13">
         <f>I31*1000000/(0.9*K31*$Z$2^2)</f>
         <v>0.1293454474</v>
       </c>
-      <c r="M31" s="13">
+      <c r="M31" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L31/(0.85*$B$2)))</f>
         <v>0.000308806777</v>
       </c>
-      <c r="N31" s="10">
+      <c r="N31" s="11">
         <f>M31*K31*$Z$2</f>
         <v>75.01534228</v>
       </c>
-      <c r="O31" s="10">
+      <c r="O31" s="11">
         <f>MAX(N31,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P31" s="14">
+      <c r="P31" s="15">
         <f>ROUNDUP(O31/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q31" s="11">
+      <c r="Q31" s="12">
         <f>O31*$D$2/(0.85*$B$2*K31)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R31" s="15" t="str">
+      <c r="R31" s="16" t="str">
         <f>IF(Q31&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S31" s="12">
+      <c r="S31" s="13">
         <f>H31*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.003407107</v>
       </c>
-      <c r="T31" s="13">
+      <c r="T31" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S31/(0.85*$B$2)))</f>
         <v>0.002441668159</v>
       </c>
-      <c r="U31" s="10">
+      <c r="U31" s="11">
         <f>T31*$H$2*1000*$Z$2</f>
         <v>111.2118805</v>
       </c>
-      <c r="V31" s="10">
+      <c r="V31" s="11">
         <f>MAX(U31,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W31" s="14">
+      <c r="W31" s="15">
         <f>ROUNDUP(V31/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X31" s="15" t="str">
+      <c r="X31" s="16" t="str">
         <f>IF(J31&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y31" s="12">
+      <c r="Y31" s="13">
         <f>D31/IF(C31="1EC",18.5,IF(C31="2EC",21,8))</f>
         <v>0.1714285714</v>
       </c>
-      <c r="Z31" s="15" t="str">
+      <c r="Z31" s="16" t="str">
         <f>IF($J$2&gt;=Y31,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -3781,105 +3895,105 @@
       <c r="B32" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="11">
         <f>IF(C32="1EC",10,IF(C32="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="11">
         <f>IF(C32="1EC",14,IF(C32="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="12">
         <f>E32*D32^2/F32</f>
         <v>4.250021236</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="12">
         <f>IF(C32="V",0,E32*D32^2/G32)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J32" s="11">
+      <c r="J32" s="12">
         <f>IF(C32="V",E32*D32,IF(C32="1EC",1.15,1)*E32*D32/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="11">
         <f>MIN(D32*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L32" s="12">
+      <c r="L32" s="13">
         <f>I32*1000000/(0.9*K32*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M32" s="13">
+      <c r="M32" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L32/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="11">
         <f>M32*K32*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O32" s="10">
+      <c r="O32" s="11">
         <f>MAX(N32,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P32" s="14">
+      <c r="P32" s="15">
         <f>ROUNDUP(O32/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q32" s="11">
+      <c r="Q32" s="12">
         <f>O32*$D$2/(0.85*$B$2*K32)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R32" s="15" t="str">
+      <c r="R32" s="16" t="str">
         <f>IF(Q32&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S32" s="12">
+      <c r="S32" s="13">
         <f>H32*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T32" s="13">
+      <c r="T32" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S32/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U32" s="10">
+      <c r="U32" s="11">
         <f>T32*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V32" s="10">
+      <c r="V32" s="11">
         <f>MAX(U32,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W32" s="14">
+      <c r="W32" s="15">
         <f>ROUNDUP(V32/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X32" s="15" t="str">
+      <c r="X32" s="16" t="str">
         <f>IF(J32&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y32" s="12">
+      <c r="Y32" s="13">
         <f>D32/IF(C32="1EC",18.5,IF(C32="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z32" s="15" t="str">
+      <c r="Z32" s="16" t="str">
         <f>IF($J$2&gt;=Y32,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -3887,99 +4001,99 @@
       <c r="B33" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="11">
         <f>IF(C33="1EC",10,IF(C33="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="11">
         <f>IF(C33="1EC",14,IF(C33="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="12">
         <f>E33*D33^2/F33</f>
         <v>4.6644224</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="12">
         <f>IF(C33="V",0,E33*D33^2/G33)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J33" s="11">
+      <c r="J33" s="12">
         <f>IF(C33="V",E33*D33,IF(C33="1EC",1.15,1)*E33*D33/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="11">
         <f>MIN(D33*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="13">
         <f>I33*1000000/(0.9*K33*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M33" s="13">
+      <c r="M33" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L33/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="11">
         <f>M33*K33*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O33" s="10">
+      <c r="O33" s="11">
         <f>MAX(N33,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P33" s="14">
+      <c r="P33" s="15">
         <f>ROUNDUP(O33/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q33" s="11">
+      <c r="Q33" s="12">
         <f>O33*$D$2/(0.85*$B$2*K33)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R33" s="15" t="str">
+      <c r="R33" s="16" t="str">
         <f>IF(Q33&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S33" s="12">
+      <c r="S33" s="13">
         <f>H33*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T33" s="13">
+      <c r="T33" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S33/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U33" s="10">
+      <c r="U33" s="11">
         <f>T33*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V33" s="10">
+      <c r="V33" s="11">
         <f>MAX(U33,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W33" s="14">
+      <c r="W33" s="15">
         <f>ROUNDUP(V33/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X33" s="15" t="str">
+      <c r="X33" s="16" t="str">
         <f>IF(J33&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y33" s="12">
+      <c r="Y33" s="13">
         <f>D33/IF(C33="1EC",18.5,IF(C33="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z33" s="15" t="str">
+      <c r="Z33" s="16" t="str">
         <f>IF($J$2&gt;=Y33,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
@@ -3993,105 +4107,105 @@
       <c r="B34" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="11">
         <f>IF(C34="1EC",10,IF(C34="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="11">
         <f>IF(C34="1EC",14,IF(C34="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="12">
         <f>E34*D34^2/F34</f>
         <v>10.17933091</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="12">
         <f>IF(C34="V",0,E34*D34^2/G34)</f>
         <v>6.99829</v>
       </c>
-      <c r="J34" s="11">
+      <c r="J34" s="12">
         <f>IF(C34="V",E34*D34,IF(C34="1EC",1.15,1)*E34*D34/2)</f>
         <v>17.22656</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="11">
         <f>MIN(D34*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="13">
         <f>I34*1000000/(0.9*K34*$Z$2^2)</f>
         <v>0.1054175377</v>
       </c>
-      <c r="M34" s="13">
+      <c r="M34" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L34/(0.85*$B$2)))</f>
         <v>0.0002515524783</v>
       </c>
-      <c r="N34" s="10">
+      <c r="N34" s="11">
         <f>M34*K34*$Z$2</f>
         <v>61.10712803</v>
       </c>
-      <c r="O34" s="10">
+      <c r="O34" s="11">
         <f>MAX(N34,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P34" s="14">
+      <c r="P34" s="15">
         <f>ROUNDUP(O34/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q34" s="11">
+      <c r="Q34" s="12">
         <f>O34*$D$2/(0.85*$B$2*K34)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R34" s="15" t="str">
+      <c r="R34" s="16" t="str">
         <f>IF(Q34&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S34" s="12">
+      <c r="S34" s="13">
         <f>H34*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.8177845346</v>
       </c>
-      <c r="T34" s="13">
+      <c r="T34" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S34/(0.85*$B$2)))</f>
         <v>0.001981759299</v>
       </c>
-      <c r="U34" s="10">
+      <c r="U34" s="11">
         <f>T34*$H$2*1000*$Z$2</f>
         <v>90.26418166</v>
       </c>
-      <c r="V34" s="10">
+      <c r="V34" s="11">
         <f>MAX(U34,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W34" s="14">
+      <c r="W34" s="15">
         <f>ROUNDUP(V34/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X34" s="15" t="str">
+      <c r="X34" s="16" t="str">
         <f>IF(J34&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y34" s="12">
+      <c r="Y34" s="13">
         <f>D34/IF(C34="1EC",18.5,IF(C34="2EC",21,8))</f>
         <v>0.1547619048</v>
       </c>
-      <c r="Z34" s="15" t="str">
+      <c r="Z34" s="16" t="str">
         <f>IF($J$2&gt;=Y34,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -4099,105 +4213,105 @@
       <c r="B35" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="11">
         <f>IF(C35="1EC",10,IF(C35="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="11">
         <f>IF(C35="1EC",14,IF(C35="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="12">
         <f>E35*D35^2/F35</f>
         <v>4.6644224</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="12">
         <f>IF(C35="V",0,E35*D35^2/G35)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J35" s="11">
+      <c r="J35" s="12">
         <f>IF(C35="V",E35*D35,IF(C35="1EC",1.15,1)*E35*D35/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="11">
         <f>MIN(D35*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L35" s="12">
+      <c r="L35" s="13">
         <f>I35*1000000/(0.9*K35*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M35" s="13">
+      <c r="M35" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L35/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N35" s="10">
+      <c r="N35" s="11">
         <f>M35*K35*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O35" s="10">
+      <c r="O35" s="11">
         <f>MAX(N35,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P35" s="14">
+      <c r="P35" s="15">
         <f>ROUNDUP(O35/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q35" s="11">
+      <c r="Q35" s="12">
         <f>O35*$D$2/(0.85*$B$2*K35)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R35" s="15" t="str">
+      <c r="R35" s="16" t="str">
         <f>IF(Q35&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S35" s="12">
+      <c r="S35" s="13">
         <f>H35*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T35" s="13">
+      <c r="T35" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S35/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U35" s="10">
+      <c r="U35" s="11">
         <f>T35*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V35" s="10">
+      <c r="V35" s="11">
         <f>MAX(U35,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W35" s="14">
+      <c r="W35" s="15">
         <f>ROUNDUP(V35/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X35" s="15" t="str">
+      <c r="X35" s="16" t="str">
         <f>IF(J35&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y35" s="12">
+      <c r="Y35" s="13">
         <f>D35/IF(C35="1EC",18.5,IF(C35="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z35" s="15" t="str">
+      <c r="Z35" s="16" t="str">
         <f>IF($J$2&gt;=Y35,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>VIGUETA 3</t>
         </is>
@@ -4205,99 +4319,99 @@
       <c r="B36" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="11">
         <f>IF(C36="1EC",10,IF(C36="2EC",11,2))</f>
         <v>2</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="11">
         <f>IF(C36="1EC",14,IF(C36="2EC",16,0))</f>
         <v>0</v>
       </c>
-      <c r="H36" s="11">
+      <c r="H36" s="12">
         <f>E36*D36^2/F36</f>
         <v>11.92608</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="12">
         <f>IF(C36="V",0,E36*D36^2/G36)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="11">
+      <c r="J36" s="12">
         <f>IF(C36="V",E36*D36,IF(C36="1EC",1.15,1)*E36*D36/2)</f>
         <v>15.90144</v>
       </c>
-      <c r="K36" s="10">
+      <c r="K36" s="11">
         <f>MIN(D36*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>375</v>
       </c>
-      <c r="L36" s="12">
+      <c r="L36" s="13">
         <f>I36*1000000/(0.9*K36*$Z$2^2)</f>
         <v>0</v>
       </c>
-      <c r="M36" s="13">
+      <c r="M36" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L36/(0.85*$B$2)))</f>
         <v>0</v>
       </c>
-      <c r="N36" s="10">
+      <c r="N36" s="11">
         <f>M36*K36*$Z$2</f>
         <v>0</v>
       </c>
-      <c r="O36" s="10">
+      <c r="O36" s="11">
         <f>MAX(N36,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P36" s="14">
+      <c r="P36" s="15">
         <f>ROUNDUP(O36/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q36" s="11">
+      <c r="Q36" s="12">
         <f>O36*$D$2/(0.85*$B$2*K36)</f>
         <v>7.144705882</v>
       </c>
-      <c r="R36" s="15" t="str">
+      <c r="R36" s="16" t="str">
         <f>IF(Q36&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S36" s="12">
+      <c r="S36" s="13">
         <f>H36*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.9581144251</v>
       </c>
-      <c r="T36" s="13">
+      <c r="T36" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S36/(0.85*$B$2)))</f>
         <v>0.002329089448</v>
       </c>
-      <c r="U36" s="10">
+      <c r="U36" s="11">
         <f>T36*$H$2*1000*$Z$2</f>
         <v>106.0842016</v>
       </c>
-      <c r="V36" s="10">
+      <c r="V36" s="11">
         <f>MAX(U36,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W36" s="14">
+      <c r="W36" s="15">
         <f>ROUNDUP(V36/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X36" s="15" t="str">
+      <c r="X36" s="16" t="str">
         <f>IF(J36&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y36" s="12">
+      <c r="Y36" s="13">
         <f>D36/IF(C36="1EC",18.5,IF(C36="2EC",21,8))</f>
         <v>0.1875</v>
       </c>
-      <c r="Z36" s="15" t="str">
+      <c r="Z36" s="16" t="str">
         <f>IF($J$2&gt;=Y36,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
@@ -4311,105 +4425,105 @@
       <c r="B37" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>1EC</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="11">
         <f>IF(C37="1EC",10,IF(C37="2EC",11,2))</f>
         <v>10</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="11">
         <f>IF(C37="1EC",14,IF(C37="2EC",16,0))</f>
         <v>14</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="12">
         <f>E37*D37^2/F37</f>
         <v>11.197264</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="12">
         <f>IF(C37="V",0,E37*D37^2/G37)</f>
         <v>7.998045714</v>
       </c>
-      <c r="J37" s="11">
+      <c r="J37" s="12">
         <f>IF(C37="V",E37*D37,IF(C37="1EC",1.15,1)*E37*D37/2)</f>
         <v>19.810544</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K37" s="11">
         <f>MIN(D37*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L37" s="12">
+      <c r="L37" s="13">
         <f>I37*1000000/(0.9*K37*$Z$2^2)</f>
         <v>0.1204771859</v>
       </c>
-      <c r="M37" s="13">
+      <c r="M37" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L37/(0.85*$B$2)))</f>
         <v>0.0002875801693</v>
       </c>
-      <c r="N37" s="10">
+      <c r="N37" s="11">
         <f>M37*K37*$Z$2</f>
         <v>69.85897472</v>
       </c>
-      <c r="O37" s="10">
+      <c r="O37" s="11">
         <f>MAX(N37,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P37" s="14">
+      <c r="P37" s="15">
         <f>ROUNDUP(O37/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q37" s="11">
+      <c r="Q37" s="12">
         <f>O37*$D$2/(0.85*$B$2*K37)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R37" s="15" t="str">
+      <c r="R37" s="16" t="str">
         <f>IF(Q37&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S37" s="12">
+      <c r="S37" s="13">
         <f>H37*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.8995629881</v>
       </c>
-      <c r="T37" s="13">
+      <c r="T37" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S37/(0.85*$B$2)))</f>
         <v>0.002183899739</v>
       </c>
-      <c r="U37" s="10">
+      <c r="U37" s="11">
         <f>T37*$H$2*1000*$Z$2</f>
         <v>99.47117335</v>
       </c>
-      <c r="V37" s="10">
+      <c r="V37" s="11">
         <f>MAX(U37,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W37" s="14">
+      <c r="W37" s="15">
         <f>ROUNDUP(V37/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X37" s="15" t="str">
+      <c r="X37" s="16" t="str">
         <f>IF(J37&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y37" s="12">
+      <c r="Y37" s="13">
         <f>D37/IF(C37="1EC",18.5,IF(C37="2EC",21,8))</f>
         <v>0.1756756757</v>
       </c>
-      <c r="Z37" s="15" t="str">
+      <c r="Z37" s="16" t="str">
         <f>IF($J$2&gt;=Y37,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 4</t>
         </is>
@@ -4417,105 +4531,105 @@
       <c r="B38" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="11">
         <f>IF(C38="1EC",10,IF(C38="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="11">
         <f>IF(C38="1EC",14,IF(C38="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="12">
         <f>E38*D38^2/F38</f>
         <v>4.6644224</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="12">
         <f>IF(C38="V",0,E38*D38^2/G38)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J38" s="11">
+      <c r="J38" s="12">
         <f>IF(C38="V",E38*D38,IF(C38="1EC",1.15,1)*E38*D38/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K38" s="10">
+      <c r="K38" s="11">
         <f>MIN(D38*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L38" s="12">
+      <c r="L38" s="13">
         <f>I38*1000000/(0.9*K38*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M38" s="13">
+      <c r="M38" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L38/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N38" s="10">
+      <c r="N38" s="11">
         <f>M38*K38*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O38" s="10">
+      <c r="O38" s="11">
         <f>MAX(N38,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P38" s="14">
+      <c r="P38" s="15">
         <f>ROUNDUP(O38/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q38" s="11">
+      <c r="Q38" s="12">
         <f>O38*$D$2/(0.85*$B$2*K38)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R38" s="15" t="str">
+      <c r="R38" s="16" t="str">
         <f>IF(Q38&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S38" s="12">
+      <c r="S38" s="13">
         <f>H38*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T38" s="13">
+      <c r="T38" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S38/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U38" s="10">
+      <c r="U38" s="11">
         <f>T38*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V38" s="10">
+      <c r="V38" s="11">
         <f>MAX(U38,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W38" s="14">
+      <c r="W38" s="15">
         <f>ROUNDUP(V38/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X38" s="15" t="str">
+      <c r="X38" s="16" t="str">
         <f>IF(J38&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y38" s="12">
+      <c r="Y38" s="13">
         <f>D38/IF(C38="1EC",18.5,IF(C38="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z38" s="15" t="str">
+      <c r="Z38" s="16" t="str">
         <f>IF($J$2&gt;=Y38,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 4</t>
         </is>
@@ -4523,105 +4637,105 @@
       <c r="B39" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="11">
         <f>IF(C39="1EC",10,IF(C39="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="11">
         <f>IF(C39="1EC",14,IF(C39="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39" s="12">
         <f>E39*D39^2/F39</f>
         <v>4.250021236</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="12">
         <f>IF(C39="V",0,E39*D39^2/G39)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J39" s="11">
+      <c r="J39" s="12">
         <f>IF(C39="V",E39*D39,IF(C39="1EC",1.15,1)*E39*D39/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="11">
         <f>MIN(D39*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L39" s="12">
+      <c r="L39" s="13">
         <f>I39*1000000/(0.9*K39*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M39" s="13">
+      <c r="M39" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L39/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N39" s="10">
+      <c r="N39" s="11">
         <f>M39*K39*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O39" s="10">
+      <c r="O39" s="11">
         <f>MAX(N39,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P39" s="14">
+      <c r="P39" s="15">
         <f>ROUNDUP(O39/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q39" s="11">
+      <c r="Q39" s="12">
         <f>O39*$D$2/(0.85*$B$2*K39)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R39" s="15" t="str">
+      <c r="R39" s="16" t="str">
         <f>IF(Q39&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S39" s="12">
+      <c r="S39" s="13">
         <f>H39*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T39" s="13">
+      <c r="T39" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S39/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U39" s="10">
+      <c r="U39" s="11">
         <f>T39*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V39" s="10">
+      <c r="V39" s="11">
         <f>MAX(U39,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W39" s="14">
+      <c r="W39" s="15">
         <f>ROUNDUP(V39/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X39" s="15" t="str">
+      <c r="X39" s="16" t="str">
         <f>IF(J39&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y39" s="12">
+      <c r="Y39" s="13">
         <f>D39/IF(C39="1EC",18.5,IF(C39="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z39" s="15" t="str">
+      <c r="Z39" s="16" t="str">
         <f>IF($J$2&gt;=Y39,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>VIGUETA 4</t>
         </is>
@@ -4629,105 +4743,105 @@
       <c r="B40" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>1EC</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="22" t="n">
         <v>3.6</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="11">
         <f>IF(C40="1EC",10,IF(C40="2EC",11,2))</f>
         <v>10</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="11">
         <f>IF(C40="1EC",14,IF(C40="2EC",16,0))</f>
         <v>14</v>
       </c>
-      <c r="H40" s="11">
+      <c r="H40" s="12">
         <f>E40*D40^2/F40</f>
         <v>13.73884416</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40" s="12">
         <f>IF(C40="V",0,E40*D40^2/G40)</f>
         <v>9.813460114</v>
       </c>
-      <c r="J40" s="11">
+      <c r="J40" s="12">
         <f>IF(C40="V",E40*D40,IF(C40="1EC",1.15,1)*E40*D40/2)</f>
         <v>21.9439872</v>
       </c>
-      <c r="K40" s="10">
+      <c r="K40" s="11">
         <f>MIN(D40*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L40" s="12">
+      <c r="L40" s="13">
         <f>I40*1000000/(0.9*K40*$Z$2^2)</f>
         <v>0.1478233685</v>
       </c>
-      <c r="M40" s="13">
+      <c r="M40" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L40/(0.85*$B$2)))</f>
         <v>0.0003530602677</v>
       </c>
-      <c r="N40" s="10">
+      <c r="N40" s="11">
         <f>M40*K40*$Z$2</f>
         <v>85.76540023</v>
       </c>
-      <c r="O40" s="10">
+      <c r="O40" s="11">
         <f>MAX(N40,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P40" s="14">
+      <c r="P40" s="15">
         <f>ROUNDUP(O40/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q40" s="11">
+      <c r="Q40" s="12">
         <f>O40*$D$2/(0.85*$B$2*K40)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R40" s="15" t="str">
+      <c r="R40" s="16" t="str">
         <f>IF(Q40&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S40" s="12">
+      <c r="S40" s="13">
         <f>H40*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.103747818</v>
       </c>
-      <c r="T40" s="13">
+      <c r="T40" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S40/(0.85*$B$2)))</f>
         <v>0.002691909619</v>
       </c>
-      <c r="U40" s="10">
+      <c r="U40" s="11">
         <f>T40*$H$2*1000*$Z$2</f>
         <v>122.6097534</v>
       </c>
-      <c r="V40" s="10">
+      <c r="V40" s="11">
         <f>MAX(U40,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W40" s="14">
+      <c r="W40" s="15">
         <f>ROUNDUP(V40/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X40" s="15" t="str">
+      <c r="X40" s="16" t="str">
         <f>IF(J40&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y40" s="12">
+      <c r="Y40" s="13">
         <f>D40/IF(C40="1EC",18.5,IF(C40="2EC",21,8))</f>
         <v>0.1945945946</v>
       </c>
-      <c r="Z40" s="15" t="str">
+      <c r="Z40" s="16" t="str">
         <f>IF($J$2&gt;=Y40,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -4735,99 +4849,99 @@
       <c r="B41" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>1EC</t>
         </is>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="11">
         <f>IF(C41="1EC",10,IF(C41="2EC",11,2))</f>
         <v>10</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="11">
         <f>IF(C41="1EC",14,IF(C41="2EC",16,0))</f>
         <v>14</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="12">
         <f>E41*D41^2/F41</f>
         <v>5.13086464</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41" s="12">
         <f>IF(C41="V",0,E41*D41^2/G41)</f>
         <v>3.664903314</v>
       </c>
-      <c r="J41" s="11">
+      <c r="J41" s="12">
         <f>IF(C41="V",E41*D41,IF(C41="1EC",1.15,1)*E41*D41/2)</f>
         <v>13.4102144</v>
       </c>
-      <c r="K41" s="10">
+      <c r="K41" s="11">
         <f>MIN(D41*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L41" s="12">
+      <c r="L41" s="13">
         <f>I41*1000000/(0.9*K41*$Z$2^2)</f>
         <v>0.08029911373</v>
       </c>
-      <c r="M41" s="13">
+      <c r="M41" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L41/(0.85*$B$2)))</f>
         <v>0.0001915119852</v>
       </c>
-      <c r="N41" s="10">
+      <c r="N41" s="11">
         <f>M41*K41*$Z$2</f>
         <v>31.98393787</v>
       </c>
-      <c r="O41" s="10">
+      <c r="O41" s="11">
         <f>MAX(N41,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P41" s="14">
+      <c r="P41" s="15">
         <f>ROUNDUP(O41/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q41" s="11">
+      <c r="Q41" s="12">
         <f>O41*$D$2/(0.85*$B$2*K41)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R41" s="15" t="str">
+      <c r="R41" s="16" t="str">
         <f>IF(Q41&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S41" s="12">
+      <c r="S41" s="13">
         <f>H41*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.4122021171</v>
       </c>
-      <c r="T41" s="13">
+      <c r="T41" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S41/(0.85*$B$2)))</f>
         <v>0.0009900830036</v>
       </c>
-      <c r="U41" s="10">
+      <c r="U41" s="11">
         <f>T41*$H$2*1000*$Z$2</f>
         <v>45.09580561</v>
       </c>
-      <c r="V41" s="10">
+      <c r="V41" s="11">
         <f>MAX(U41,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W41" s="14">
+      <c r="W41" s="15">
         <f>ROUNDUP(V41/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X41" s="15" t="str">
+      <c r="X41" s="16" t="str">
         <f>IF(J41&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y41" s="12">
+      <c r="Y41" s="13">
         <f>D41/IF(C41="1EC",18.5,IF(C41="2EC",21,8))</f>
         <v>0.1189189189</v>
       </c>
-      <c r="Z41" s="15" t="str">
+      <c r="Z41" s="16" t="str">
         <f>IF($J$2&gt;=Y41,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
@@ -4841,105 +4955,105 @@
       <c r="B42" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="11">
         <f>IF(C42="1EC",10,IF(C42="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="11">
         <f>IF(C42="1EC",14,IF(C42="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H42" s="11">
+      <c r="H42" s="12">
         <f>E42*D42^2/F42</f>
         <v>10.17933091</v>
       </c>
-      <c r="I42" s="11">
+      <c r="I42" s="12">
         <f>IF(C42="V",0,E42*D42^2/G42)</f>
         <v>6.99829</v>
       </c>
-      <c r="J42" s="11">
+      <c r="J42" s="12">
         <f>IF(C42="V",E42*D42,IF(C42="1EC",1.15,1)*E42*D42/2)</f>
         <v>17.22656</v>
       </c>
-      <c r="K42" s="10">
+      <c r="K42" s="11">
         <f>MIN(D42*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L42" s="12">
+      <c r="L42" s="13">
         <f>I42*1000000/(0.9*K42*$Z$2^2)</f>
         <v>0.1054175377</v>
       </c>
-      <c r="M42" s="13">
+      <c r="M42" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L42/(0.85*$B$2)))</f>
         <v>0.0002515524783</v>
       </c>
-      <c r="N42" s="10">
+      <c r="N42" s="11">
         <f>M42*K42*$Z$2</f>
         <v>61.10712803</v>
       </c>
-      <c r="O42" s="10">
+      <c r="O42" s="11">
         <f>MAX(N42,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P42" s="14">
+      <c r="P42" s="15">
         <f>ROUNDUP(O42/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q42" s="11">
+      <c r="Q42" s="12">
         <f>O42*$D$2/(0.85*$B$2*K42)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R42" s="15" t="str">
+      <c r="R42" s="16" t="str">
         <f>IF(Q42&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S42" s="12">
+      <c r="S42" s="13">
         <f>H42*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.8177845346</v>
       </c>
-      <c r="T42" s="13">
+      <c r="T42" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S42/(0.85*$B$2)))</f>
         <v>0.001981759299</v>
       </c>
-      <c r="U42" s="10">
+      <c r="U42" s="11">
         <f>T42*$H$2*1000*$Z$2</f>
         <v>90.26418166</v>
       </c>
-      <c r="V42" s="10">
+      <c r="V42" s="11">
         <f>MAX(U42,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W42" s="14">
+      <c r="W42" s="15">
         <f>ROUNDUP(V42/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X42" s="15" t="str">
+      <c r="X42" s="16" t="str">
         <f>IF(J42&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y42" s="12">
+      <c r="Y42" s="13">
         <f>D42/IF(C42="1EC",18.5,IF(C42="2EC",21,8))</f>
         <v>0.1547619048</v>
       </c>
-      <c r="Z42" s="15" t="str">
+      <c r="Z42" s="16" t="str">
         <f>IF($J$2&gt;=Y42,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -4947,105 +5061,105 @@
       <c r="B43" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D43" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="11">
         <f>IF(C43="1EC",10,IF(C43="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43" s="11">
         <f>IF(C43="1EC",14,IF(C43="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H43" s="12">
         <f>E43*D43^2/F43</f>
         <v>4.6644224</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="12">
         <f>IF(C43="V",0,E43*D43^2/G43)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J43" s="11">
+      <c r="J43" s="12">
         <f>IF(C43="V",E43*D43,IF(C43="1EC",1.15,1)*E43*D43/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K43" s="10">
+      <c r="K43" s="11">
         <f>MIN(D43*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L43" s="12">
+      <c r="L43" s="13">
         <f>I43*1000000/(0.9*K43*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M43" s="13">
+      <c r="M43" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L43/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N43" s="10">
+      <c r="N43" s="11">
         <f>M43*K43*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O43" s="10">
+      <c r="O43" s="11">
         <f>MAX(N43,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P43" s="14">
+      <c r="P43" s="15">
         <f>ROUNDUP(O43/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q43" s="11">
+      <c r="Q43" s="12">
         <f>O43*$D$2/(0.85*$B$2*K43)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R43" s="15" t="str">
+      <c r="R43" s="16" t="str">
         <f>IF(Q43&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S43" s="12">
+      <c r="S43" s="13">
         <f>H43*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T43" s="13">
+      <c r="T43" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S43/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U43" s="10">
+      <c r="U43" s="11">
         <f>T43*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V43" s="10">
+      <c r="V43" s="11">
         <f>MAX(U43,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W43" s="14">
+      <c r="W43" s="15">
         <f>ROUNDUP(V43/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X43" s="15" t="str">
+      <c r="X43" s="16" t="str">
         <f>IF(J43&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y43" s="12">
+      <c r="Y43" s="13">
         <f>D43/IF(C43="1EC",18.5,IF(C43="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z43" s="15" t="str">
+      <c r="Z43" s="16" t="str">
         <f>IF($J$2&gt;=Y43,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -5053,105 +5167,105 @@
       <c r="B44" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="D44" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="11">
         <f>IF(C44="1EC",10,IF(C44="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44" s="11">
         <f>IF(C44="1EC",14,IF(C44="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H44" s="11">
+      <c r="H44" s="12">
         <f>E44*D44^2/F44</f>
         <v>4.250021236</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="12">
         <f>IF(C44="V",0,E44*D44^2/G44)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J44" s="11">
+      <c r="J44" s="12">
         <f>IF(C44="V",E44*D44,IF(C44="1EC",1.15,1)*E44*D44/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K44" s="10">
+      <c r="K44" s="11">
         <f>MIN(D44*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L44" s="12">
+      <c r="L44" s="13">
         <f>I44*1000000/(0.9*K44*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M44" s="13">
+      <c r="M44" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L44/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N44" s="10">
+      <c r="N44" s="11">
         <f>M44*K44*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O44" s="10">
+      <c r="O44" s="11">
         <f>MAX(N44,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P44" s="14">
+      <c r="P44" s="15">
         <f>ROUNDUP(O44/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q44" s="11">
+      <c r="Q44" s="12">
         <f>O44*$D$2/(0.85*$B$2*K44)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R44" s="15" t="str">
+      <c r="R44" s="16" t="str">
         <f>IF(Q44&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S44" s="12">
+      <c r="S44" s="13">
         <f>H44*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T44" s="13">
+      <c r="T44" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S44/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U44" s="10">
+      <c r="U44" s="11">
         <f>T44*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V44" s="10">
+      <c r="V44" s="11">
         <f>MAX(U44,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W44" s="14">
+      <c r="W44" s="15">
         <f>ROUNDUP(V44/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X44" s="15" t="str">
+      <c r="X44" s="16" t="str">
         <f>IF(J44&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y44" s="12">
+      <c r="Y44" s="13">
         <f>D44/IF(C44="1EC",18.5,IF(C44="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z44" s="15" t="str">
+      <c r="Z44" s="16" t="str">
         <f>IF($J$2&gt;=Y44,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -5159,105 +5273,105 @@
       <c r="B45" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D45" s="28" t="n">
         <v>3.8</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="11">
         <f>IF(C45="1EC",10,IF(C45="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="11">
         <f>IF(C45="1EC",14,IF(C45="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="12">
         <f>E45*D45^2/F45</f>
         <v>13.91616931</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="12">
         <f>IF(C45="V",0,E45*D45^2/G45)</f>
         <v>9.5673664</v>
       </c>
-      <c r="J45" s="11">
+      <c r="J45" s="12">
         <f>IF(C45="V",E45*D45,IF(C45="1EC",1.15,1)*E45*D45/2)</f>
         <v>20.141824</v>
       </c>
-      <c r="K45" s="10">
+      <c r="K45" s="11">
         <f>MIN(D45*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L45" s="12">
+      <c r="L45" s="13">
         <f>I45*1000000/(0.9*K45*$Z$2^2)</f>
         <v>0.1441163781</v>
       </c>
-      <c r="M45" s="13">
+      <c r="M45" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L45/(0.85*$B$2)))</f>
         <v>0.0003441794645</v>
       </c>
-      <c r="N45" s="10">
+      <c r="N45" s="11">
         <f>M45*K45*$Z$2</f>
         <v>83.60807552</v>
       </c>
-      <c r="O45" s="10">
+      <c r="O45" s="11">
         <f>MAX(N45,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P45" s="14">
+      <c r="P45" s="15">
         <f>ROUNDUP(O45/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q45" s="11">
+      <c r="Q45" s="12">
         <f>O45*$D$2/(0.85*$B$2*K45)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R45" s="15" t="str">
+      <c r="R45" s="16" t="str">
         <f>IF(Q45&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S45" s="12">
+      <c r="S45" s="13">
         <f>H45*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.117993721</v>
       </c>
-      <c r="T45" s="13">
+      <c r="T45" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S45/(0.85*$B$2)))</f>
         <v>0.002727531841</v>
       </c>
-      <c r="U45" s="10">
+      <c r="U45" s="11">
         <f>T45*$H$2*1000*$Z$2</f>
         <v>124.2322565</v>
       </c>
-      <c r="V45" s="10">
+      <c r="V45" s="11">
         <f>MAX(U45,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W45" s="14">
+      <c r="W45" s="15">
         <f>ROUNDUP(V45/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X45" s="15" t="str">
+      <c r="X45" s="16" t="str">
         <f>IF(J45&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y45" s="12">
+      <c r="Y45" s="13">
         <f>D45/IF(C45="1EC",18.5,IF(C45="2EC",21,8))</f>
         <v>0.180952381</v>
       </c>
-      <c r="Z45" s="15" t="str">
+      <c r="Z45" s="16" t="str">
         <f>IF($J$2&gt;=Y45,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -5265,105 +5379,105 @@
       <c r="B46" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D46" s="8" t="n">
+      <c r="D46" s="30" t="n">
         <v>2.4</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="11">
         <f>IF(C46="1EC",10,IF(C46="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="11">
         <f>IF(C46="1EC",14,IF(C46="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H46" s="11">
+      <c r="H46" s="12">
         <f>E46*D46^2/F46</f>
         <v>5.551048145</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="12">
         <f>IF(C46="V",0,E46*D46^2/G46)</f>
         <v>3.8163456</v>
       </c>
-      <c r="J46" s="11">
+      <c r="J46" s="12">
         <f>IF(C46="V",E46*D46,IF(C46="1EC",1.15,1)*E46*D46/2)</f>
         <v>12.721152</v>
       </c>
-      <c r="K46" s="10">
+      <c r="K46" s="11">
         <f>MIN(D46*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>600</v>
       </c>
-      <c r="L46" s="12">
+      <c r="L46" s="13">
         <f>I46*1000000/(0.9*K46*$Z$2^2)</f>
         <v>0.07664915401</v>
       </c>
-      <c r="M46" s="13">
+      <c r="M46" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L46/(0.85*$B$2)))</f>
         <v>0.0001827928082</v>
       </c>
-      <c r="N46" s="10">
+      <c r="N46" s="11">
         <f>M46*K46*$Z$2</f>
         <v>33.30302172</v>
       </c>
-      <c r="O46" s="10">
+      <c r="O46" s="11">
         <f>MAX(N46,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P46" s="14">
+      <c r="P46" s="15">
         <f>ROUNDUP(O46/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q46" s="11">
+      <c r="Q46" s="12">
         <f>O46*$D$2/(0.85*$B$2*K46)</f>
         <v>4.465441176</v>
       </c>
-      <c r="R46" s="15" t="str">
+      <c r="R46" s="16" t="str">
         <f>IF(Q46&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S46" s="12">
+      <c r="S46" s="13">
         <f>H46*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.4459587142</v>
       </c>
-      <c r="T46" s="13">
+      <c r="T46" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S46/(0.85*$B$2)))</f>
         <v>0.001071945286</v>
       </c>
-      <c r="U46" s="10">
+      <c r="U46" s="11">
         <f>T46*$H$2*1000*$Z$2</f>
         <v>48.82442793</v>
       </c>
-      <c r="V46" s="10">
+      <c r="V46" s="11">
         <f>MAX(U46,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W46" s="14">
+      <c r="W46" s="15">
         <f>ROUNDUP(V46/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X46" s="15" t="str">
+      <c r="X46" s="16" t="str">
         <f>IF(J46&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y46" s="12">
+      <c r="Y46" s="13">
         <f>D46/IF(C46="1EC",18.5,IF(C46="2EC",21,8))</f>
         <v>0.1142857143</v>
       </c>
-      <c r="Z46" s="15" t="str">
+      <c r="Z46" s="16" t="str">
         <f>IF($J$2&gt;=Y46,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="31" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -5371,105 +5485,105 @@
       <c r="B47" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n">
+      <c r="D47" s="32" t="n">
         <v>2.3</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="11">
         <f>IF(C47="1EC",10,IF(C47="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="11">
         <f>IF(C47="1EC",14,IF(C47="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="12">
         <f>E47*D47^2/F47</f>
         <v>5.098098036</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="12">
         <f>IF(C47="V",0,E47*D47^2/G47)</f>
         <v>3.5049424</v>
       </c>
-      <c r="J47" s="11">
+      <c r="J47" s="12">
         <f>IF(C47="V",E47*D47,IF(C47="1EC",1.15,1)*E47*D47/2)</f>
         <v>12.191104</v>
       </c>
-      <c r="K47" s="10">
+      <c r="K47" s="11">
         <f>MIN(D47*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>575</v>
       </c>
-      <c r="L47" s="12">
+      <c r="L47" s="13">
         <f>I47*1000000/(0.9*K47*$Z$2^2)</f>
         <v>0.07345543926</v>
       </c>
-      <c r="M47" s="13">
+      <c r="M47" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L47/(0.85*$B$2)))</f>
         <v>0.0001751646323</v>
       </c>
-      <c r="N47" s="10">
+      <c r="N47" s="11">
         <f>M47*K47*$Z$2</f>
         <v>30.58352584</v>
       </c>
-      <c r="O47" s="10">
+      <c r="O47" s="11">
         <f>MAX(N47,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P47" s="14">
+      <c r="P47" s="15">
         <f>ROUNDUP(O47/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q47" s="11">
+      <c r="Q47" s="12">
         <f>O47*$D$2/(0.85*$B$2*K47)</f>
         <v>4.659590793</v>
       </c>
-      <c r="R47" s="15" t="str">
+      <c r="R47" s="16" t="str">
         <f>IF(Q47&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S47" s="12">
+      <c r="S47" s="13">
         <f>H47*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.4095697219</v>
       </c>
-      <c r="T47" s="13">
+      <c r="T47" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S47/(0.85*$B$2)))</f>
         <v>0.000983704306</v>
       </c>
-      <c r="U47" s="10">
+      <c r="U47" s="11">
         <f>T47*$H$2*1000*$Z$2</f>
         <v>44.80527188</v>
       </c>
-      <c r="V47" s="10">
+      <c r="V47" s="11">
         <f>MAX(U47,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W47" s="14">
+      <c r="W47" s="15">
         <f>ROUNDUP(V47/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X47" s="15" t="str">
+      <c r="X47" s="16" t="str">
         <f>IF(J47&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y47" s="12">
+      <c r="Y47" s="13">
         <f>D47/IF(C47="1EC",18.5,IF(C47="2EC",21,8))</f>
         <v>0.1095238095</v>
       </c>
-      <c r="Z47" s="15" t="str">
+      <c r="Z47" s="16" t="str">
         <f>IF($J$2&gt;=Y47,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -5477,105 +5591,105 @@
       <c r="B48" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D48" s="8" t="n">
+      <c r="D48" s="28" t="n">
         <v>3.8</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="11">
         <f>IF(C48="1EC",10,IF(C48="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="11">
         <f>IF(C48="1EC",14,IF(C48="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="12">
         <f>E48*D48^2/F48</f>
         <v>13.91616931</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48" s="12">
         <f>IF(C48="V",0,E48*D48^2/G48)</f>
         <v>9.5673664</v>
       </c>
-      <c r="J48" s="11">
+      <c r="J48" s="12">
         <f>IF(C48="V",E48*D48,IF(C48="1EC",1.15,1)*E48*D48/2)</f>
         <v>20.141824</v>
       </c>
-      <c r="K48" s="10">
+      <c r="K48" s="11">
         <f>MIN(D48*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L48" s="12">
+      <c r="L48" s="13">
         <f>I48*1000000/(0.9*K48*$Z$2^2)</f>
         <v>0.1441163781</v>
       </c>
-      <c r="M48" s="13">
+      <c r="M48" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L48/(0.85*$B$2)))</f>
         <v>0.0003441794645</v>
       </c>
-      <c r="N48" s="10">
+      <c r="N48" s="11">
         <f>M48*K48*$Z$2</f>
         <v>83.60807552</v>
       </c>
-      <c r="O48" s="10">
+      <c r="O48" s="11">
         <f>MAX(N48,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P48" s="14">
+      <c r="P48" s="15">
         <f>ROUNDUP(O48/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q48" s="11">
+      <c r="Q48" s="12">
         <f>O48*$D$2/(0.85*$B$2*K48)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R48" s="15" t="str">
+      <c r="R48" s="16" t="str">
         <f>IF(Q48&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S48" s="12">
+      <c r="S48" s="13">
         <f>H48*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.117993721</v>
       </c>
-      <c r="T48" s="13">
+      <c r="T48" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S48/(0.85*$B$2)))</f>
         <v>0.002727531841</v>
       </c>
-      <c r="U48" s="10">
+      <c r="U48" s="11">
         <f>T48*$H$2*1000*$Z$2</f>
         <v>124.2322565</v>
       </c>
-      <c r="V48" s="10">
+      <c r="V48" s="11">
         <f>MAX(U48,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W48" s="14">
+      <c r="W48" s="15">
         <f>ROUNDUP(V48/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X48" s="15" t="str">
+      <c r="X48" s="16" t="str">
         <f>IF(J48&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y48" s="12">
+      <c r="Y48" s="13">
         <f>D48/IF(C48="1EC",18.5,IF(C48="2EC",21,8))</f>
         <v>0.180952381</v>
       </c>
-      <c r="Z48" s="15" t="str">
+      <c r="Z48" s="16" t="str">
         <f>IF($J$2&gt;=Y48,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -5583,105 +5697,105 @@
       <c r="B49" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D49" s="8" t="n">
+      <c r="D49" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="11">
         <f>IF(C49="1EC",10,IF(C49="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="11">
         <f>IF(C49="1EC",14,IF(C49="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="12">
         <f>E49*D49^2/F49</f>
         <v>4.250021236</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="12">
         <f>IF(C49="V",0,E49*D49^2/G49)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J49" s="11">
+      <c r="J49" s="12">
         <f>IF(C49="V",E49*D49,IF(C49="1EC",1.15,1)*E49*D49/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K49" s="10">
+      <c r="K49" s="11">
         <f>MIN(D49*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L49" s="12">
+      <c r="L49" s="13">
         <f>I49*1000000/(0.9*K49*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M49" s="13">
+      <c r="M49" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L49/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N49" s="10">
+      <c r="N49" s="11">
         <f>M49*K49*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O49" s="10">
+      <c r="O49" s="11">
         <f>MAX(N49,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P49" s="14">
+      <c r="P49" s="15">
         <f>ROUNDUP(O49/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q49" s="11">
+      <c r="Q49" s="12">
         <f>O49*$D$2/(0.85*$B$2*K49)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R49" s="15" t="str">
+      <c r="R49" s="16" t="str">
         <f>IF(Q49&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S49" s="12">
+      <c r="S49" s="13">
         <f>H49*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T49" s="13">
+      <c r="T49" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S49/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U49" s="10">
+      <c r="U49" s="11">
         <f>T49*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V49" s="10">
+      <c r="V49" s="11">
         <f>MAX(U49,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W49" s="14">
+      <c r="W49" s="15">
         <f>ROUNDUP(V49/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X49" s="15" t="str">
+      <c r="X49" s="16" t="str">
         <f>IF(J49&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y49" s="12">
+      <c r="Y49" s="13">
         <f>D49/IF(C49="1EC",18.5,IF(C49="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z49" s="15" t="str">
+      <c r="Z49" s="16" t="str">
         <f>IF($J$2&gt;=Y49,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -5689,99 +5803,99 @@
       <c r="B50" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D50" s="8" t="n">
+      <c r="D50" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="11">
         <f>IF(C50="1EC",10,IF(C50="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="11">
         <f>IF(C50="1EC",14,IF(C50="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H50" s="12">
         <f>E50*D50^2/F50</f>
         <v>4.6644224</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50" s="12">
         <f>IF(C50="V",0,E50*D50^2/G50)</f>
         <v>3.2067904</v>
       </c>
-      <c r="J50" s="11">
+      <c r="J50" s="12">
         <f>IF(C50="V",E50*D50,IF(C50="1EC",1.15,1)*E50*D50/2)</f>
         <v>11.661056</v>
       </c>
-      <c r="K50" s="10">
+      <c r="K50" s="11">
         <f>MIN(D50*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L50" s="12">
+      <c r="L50" s="13">
         <f>I50*1000000/(0.9*K50*$Z$2^2)</f>
         <v>0.07026172451</v>
       </c>
-      <c r="M50" s="13">
+      <c r="M50" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L50/(0.85*$B$2)))</f>
         <v>0.0001675374862</v>
       </c>
-      <c r="N50" s="10">
+      <c r="N50" s="11">
         <f>M50*K50*$Z$2</f>
         <v>27.98001673</v>
       </c>
-      <c r="O50" s="10">
+      <c r="O50" s="11">
         <f>MAX(N50,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P50" s="14">
+      <c r="P50" s="15">
         <f>ROUNDUP(O50/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q50" s="11">
+      <c r="Q50" s="12">
         <f>O50*$D$2/(0.85*$B$2*K50)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R50" s="15" t="str">
+      <c r="R50" s="16" t="str">
         <f>IF(Q50&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S50" s="12">
+      <c r="S50" s="13">
         <f>H50*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3747291974</v>
       </c>
-      <c r="T50" s="13">
+      <c r="T50" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S50/(0.85*$B$2)))</f>
         <v>0.0008993490995</v>
       </c>
-      <c r="U50" s="10">
+      <c r="U50" s="11">
         <f>T50*$H$2*1000*$Z$2</f>
         <v>40.96310311</v>
       </c>
-      <c r="V50" s="10">
+      <c r="V50" s="11">
         <f>MAX(U50,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W50" s="14">
+      <c r="W50" s="15">
         <f>ROUNDUP(V50/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X50" s="15" t="str">
+      <c r="X50" s="16" t="str">
         <f>IF(J50&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y50" s="12">
+      <c r="Y50" s="13">
         <f>D50/IF(C50="1EC",18.5,IF(C50="2EC",21,8))</f>
         <v>0.1047619048</v>
       </c>
-      <c r="Z50" s="15" t="str">
+      <c r="Z50" s="16" t="str">
         <f>IF($J$2&gt;=Y50,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
@@ -5795,105 +5909,105 @@
       <c r="B51" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D51" s="8" t="n">
+      <c r="D51" s="9" t="n">
         <v>3.25</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="11">
         <f>IF(C51="1EC",10,IF(C51="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="11">
         <f>IF(C51="1EC",14,IF(C51="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="12">
         <f>E51*D51^2/F51</f>
         <v>10.17933091</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="12">
         <f>IF(C51="V",0,E51*D51^2/G51)</f>
         <v>6.99829</v>
       </c>
-      <c r="J51" s="11">
+      <c r="J51" s="12">
         <f>IF(C51="V",E51*D51,IF(C51="1EC",1.15,1)*E51*D51/2)</f>
         <v>17.22656</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K51" s="11">
         <f>MIN(D51*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L51" s="12">
+      <c r="L51" s="13">
         <f>I51*1000000/(0.9*K51*$Z$2^2)</f>
         <v>0.1054175377</v>
       </c>
-      <c r="M51" s="13">
+      <c r="M51" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L51/(0.85*$B$2)))</f>
         <v>0.0002515524783</v>
       </c>
-      <c r="N51" s="10">
+      <c r="N51" s="11">
         <f>M51*K51*$Z$2</f>
         <v>61.10712803</v>
       </c>
-      <c r="O51" s="10">
+      <c r="O51" s="11">
         <f>MAX(N51,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P51" s="14">
+      <c r="P51" s="15">
         <f>ROUNDUP(O51/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q51" s="11">
+      <c r="Q51" s="12">
         <f>O51*$D$2/(0.85*$B$2*K51)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R51" s="15" t="str">
+      <c r="R51" s="16" t="str">
         <f>IF(Q51&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S51" s="12">
+      <c r="S51" s="13">
         <f>H51*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.8177845346</v>
       </c>
-      <c r="T51" s="13">
+      <c r="T51" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S51/(0.85*$B$2)))</f>
         <v>0.001981759299</v>
       </c>
-      <c r="U51" s="10">
+      <c r="U51" s="11">
         <f>T51*$H$2*1000*$Z$2</f>
         <v>90.26418166</v>
       </c>
-      <c r="V51" s="10">
+      <c r="V51" s="11">
         <f>MAX(U51,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W51" s="14">
+      <c r="W51" s="15">
         <f>ROUNDUP(V51/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X51" s="15" t="str">
+      <c r="X51" s="16" t="str">
         <f>IF(J51&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y51" s="12">
+      <c r="Y51" s="13">
         <f>D51/IF(C51="1EC",18.5,IF(C51="2EC",21,8))</f>
         <v>0.1547619048</v>
       </c>
-      <c r="Z51" s="15" t="str">
+      <c r="Z51" s="16" t="str">
         <f>IF($J$2&gt;=Y51,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>VIGUETA 5</t>
         </is>
@@ -5901,105 +6015,105 @@
       <c r="B52" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>1EC</t>
         </is>
       </c>
-      <c r="D52" s="8" t="n">
+      <c r="D52" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="11">
         <f>IF(C52="1EC",10,IF(C52="2EC",11,2))</f>
         <v>10</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="11">
         <f>IF(C52="1EC",14,IF(C52="2EC",16,0))</f>
         <v>14</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="12">
         <f>E52*D52^2/F52</f>
         <v>5.13086464</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="12">
         <f>IF(C52="V",0,E52*D52^2/G52)</f>
         <v>3.664903314</v>
       </c>
-      <c r="J52" s="11">
+      <c r="J52" s="12">
         <f>IF(C52="V",E52*D52,IF(C52="1EC",1.15,1)*E52*D52/2)</f>
         <v>13.4102144</v>
       </c>
-      <c r="K52" s="10">
+      <c r="K52" s="11">
         <f>MIN(D52*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>550</v>
       </c>
-      <c r="L52" s="12">
+      <c r="L52" s="13">
         <f>I52*1000000/(0.9*K52*$Z$2^2)</f>
         <v>0.08029911373</v>
       </c>
-      <c r="M52" s="13">
+      <c r="M52" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L52/(0.85*$B$2)))</f>
         <v>0.0001915119852</v>
       </c>
-      <c r="N52" s="10">
+      <c r="N52" s="11">
         <f>M52*K52*$Z$2</f>
         <v>31.98393787</v>
       </c>
-      <c r="O52" s="10">
+      <c r="O52" s="11">
         <f>MAX(N52,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P52" s="14">
+      <c r="P52" s="15">
         <f>ROUNDUP(O52/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q52" s="11">
+      <c r="Q52" s="12">
         <f>O52*$D$2/(0.85*$B$2*K52)</f>
         <v>4.871390374</v>
       </c>
-      <c r="R52" s="15" t="str">
+      <c r="R52" s="16" t="str">
         <f>IF(Q52&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S52" s="12">
+      <c r="S52" s="13">
         <f>H52*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.4122021171</v>
       </c>
-      <c r="T52" s="13">
+      <c r="T52" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S52/(0.85*$B$2)))</f>
         <v>0.0009900830036</v>
       </c>
-      <c r="U52" s="10">
+      <c r="U52" s="11">
         <f>T52*$H$2*1000*$Z$2</f>
         <v>45.09580561</v>
       </c>
-      <c r="V52" s="10">
+      <c r="V52" s="11">
         <f>MAX(U52,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W52" s="14">
+      <c r="W52" s="15">
         <f>ROUNDUP(V52/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X52" s="15" t="str">
+      <c r="X52" s="16" t="str">
         <f>IF(J52&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y52" s="12">
+      <c r="Y52" s="13">
         <f>D52/IF(C52="1EC",18.5,IF(C52="2EC",21,8))</f>
         <v>0.1189189189</v>
       </c>
-      <c r="Z52" s="15" t="str">
+      <c r="Z52" s="16" t="str">
         <f>IF($J$2&gt;=Y52,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6007,105 +6121,105 @@
       <c r="B53" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D53" s="8" t="n">
+      <c r="D53" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53" s="11">
         <f>IF(C53="1EC",10,IF(C53="2EC",11,2))</f>
         <v>2</v>
       </c>
-      <c r="G53" s="10">
+      <c r="G53" s="11">
         <f>IF(C53="1EC",14,IF(C53="2EC",16,0))</f>
         <v>0</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="12">
         <f>E53*D53^2/F53</f>
         <v>11.92608</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="12">
         <f>IF(C53="V",0,E53*D53^2/G53)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="11">
+      <c r="J53" s="12">
         <f>IF(C53="V",E53*D53,IF(C53="1EC",1.15,1)*E53*D53/2)</f>
         <v>15.90144</v>
       </c>
-      <c r="K53" s="10">
+      <c r="K53" s="11">
         <f>MIN(D53*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>375</v>
       </c>
-      <c r="L53" s="12">
+      <c r="L53" s="13">
         <f>I53*1000000/(0.9*K53*$Z$2^2)</f>
         <v>0</v>
       </c>
-      <c r="M53" s="13">
+      <c r="M53" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L53/(0.85*$B$2)))</f>
         <v>0</v>
       </c>
-      <c r="N53" s="10">
+      <c r="N53" s="11">
         <f>M53*K53*$Z$2</f>
         <v>0</v>
       </c>
-      <c r="O53" s="10">
+      <c r="O53" s="11">
         <f>MAX(N53,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P53" s="14">
+      <c r="P53" s="15">
         <f>ROUNDUP(O53/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q53" s="11">
+      <c r="Q53" s="12">
         <f>O53*$D$2/(0.85*$B$2*K53)</f>
         <v>7.144705882</v>
       </c>
-      <c r="R53" s="15" t="str">
+      <c r="R53" s="16" t="str">
         <f>IF(Q53&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S53" s="12">
+      <c r="S53" s="13">
         <f>H53*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.9581144251</v>
       </c>
-      <c r="T53" s="13">
+      <c r="T53" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S53/(0.85*$B$2)))</f>
         <v>0.002329089448</v>
       </c>
-      <c r="U53" s="10">
+      <c r="U53" s="11">
         <f>T53*$H$2*1000*$Z$2</f>
         <v>106.0842016</v>
       </c>
-      <c r="V53" s="10">
+      <c r="V53" s="11">
         <f>MAX(U53,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W53" s="14">
+      <c r="W53" s="15">
         <f>ROUNDUP(V53/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X53" s="15" t="str">
+      <c r="X53" s="16" t="str">
         <f>IF(J53&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y53" s="12">
+      <c r="Y53" s="13">
         <f>D53/IF(C53="1EC",18.5,IF(C53="2EC",21,8))</f>
         <v>0.1875</v>
       </c>
-      <c r="Z53" s="15" t="str">
+      <c r="Z53" s="16" t="str">
         <f>IF($J$2&gt;=Y53,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="33" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6113,105 +6227,105 @@
       <c r="B54" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D54" s="8" t="n">
+      <c r="D54" s="34" t="n">
         <v>4.8</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F54" s="11">
         <f>IF(C54="1EC",10,IF(C54="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G54" s="11">
         <f>IF(C54="1EC",14,IF(C54="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H54" s="11">
+      <c r="H54" s="12">
         <f>E54*D54^2/F54</f>
         <v>22.20419258</v>
       </c>
-      <c r="I54" s="11">
+      <c r="I54" s="12">
         <f>IF(C54="V",0,E54*D54^2/G54)</f>
         <v>15.2653824</v>
       </c>
-      <c r="J54" s="11">
+      <c r="J54" s="12">
         <f>IF(C54="V",E54*D54,IF(C54="1EC",1.15,1)*E54*D54/2)</f>
         <v>25.442304</v>
       </c>
-      <c r="K54" s="10">
+      <c r="K54" s="11">
         <f>MIN(D54*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L54" s="12">
+      <c r="L54" s="13">
         <f>I54*1000000/(0.9*K54*$Z$2^2)</f>
         <v>0.229947462</v>
       </c>
-      <c r="M54" s="13">
+      <c r="M54" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L54/(0.85*$B$2)))</f>
         <v>0.0005501646734</v>
       </c>
-      <c r="N54" s="10">
+      <c r="N54" s="11">
         <f>M54*K54*$Z$2</f>
         <v>133.6460025</v>
       </c>
-      <c r="O54" s="10">
+      <c r="O54" s="11">
         <f>MAX(N54,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P54" s="14">
+      <c r="P54" s="15">
         <f>ROUNDUP(O54/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q54" s="11">
+      <c r="Q54" s="12">
         <f>O54*$D$2/(0.85*$B$2*K54)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R54" s="15" t="str">
+      <c r="R54" s="16" t="str">
         <f>IF(Q54&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S54" s="12">
+      <c r="S54" s="13">
         <f>H54*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.783834857</v>
       </c>
-      <c r="T54" s="13">
+      <c r="T54" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S54/(0.85*$B$2)))</f>
         <v>0.004419572507</v>
       </c>
-      <c r="U54" s="10">
+      <c r="U54" s="11">
         <f>T54*$H$2*1000*$Z$2</f>
         <v>201.3004788</v>
       </c>
-      <c r="V54" s="10">
+      <c r="V54" s="11">
         <f>MAX(U54,$AB$2)</f>
         <v>201.3004788</v>
       </c>
-      <c r="W54" s="14">
+      <c r="W54" s="15">
         <f>ROUNDUP(V54/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X54" s="15" t="str">
+      <c r="X54" s="16" t="str">
         <f>IF(J54&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y54" s="12">
+      <c r="Y54" s="13">
         <f>D54/IF(C54="1EC",18.5,IF(C54="2EC",21,8))</f>
         <v>0.2285714286</v>
       </c>
-      <c r="Z54" s="15" t="str">
+      <c r="Z54" s="16" t="str">
         <f>IF($J$2&gt;=Y54,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6219,105 +6333,105 @@
       <c r="B55" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D55" s="8" t="n">
+      <c r="D55" s="36" t="n">
         <v>5.15</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F55" s="10">
+      <c r="F55" s="11">
         <f>IF(C55="1EC",10,IF(C55="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G55" s="10">
+      <c r="G55" s="11">
         <f>IF(C55="1EC",14,IF(C55="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H55" s="11">
+      <c r="H55" s="12">
         <f>E55*D55^2/F55</f>
         <v>25.56036015</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="12">
         <f>IF(C55="V",0,E55*D55^2/G55)</f>
         <v>17.5727476</v>
       </c>
-      <c r="J55" s="11">
+      <c r="J55" s="12">
         <f>IF(C55="V",E55*D55,IF(C55="1EC",1.15,1)*E55*D55/2)</f>
         <v>27.297472</v>
       </c>
-      <c r="K55" s="10">
+      <c r="K55" s="11">
         <f>MIN(D55*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L55" s="12">
+      <c r="L55" s="13">
         <f>I55*1000000/(0.9*K55*$Z$2^2)</f>
         <v>0.2647040608</v>
       </c>
-      <c r="M55" s="13">
+      <c r="M55" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L55/(0.85*$B$2)))</f>
         <v>0.0006337921089</v>
       </c>
-      <c r="N55" s="10">
+      <c r="N55" s="11">
         <f>M55*K55*$Z$2</f>
         <v>153.9607791</v>
       </c>
-      <c r="O55" s="10">
+      <c r="O55" s="11">
         <f>MAX(N55,$AB$2)</f>
         <v>153.9607791</v>
       </c>
-      <c r="P55" s="14">
+      <c r="P55" s="15">
         <f>ROUNDUP(O55/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q55" s="11">
+      <c r="Q55" s="12">
         <f>O55*$D$2/(0.85*$B$2*K55)</f>
         <v>3.396193657</v>
       </c>
-      <c r="R55" s="15" t="str">
+      <c r="R55" s="16" t="str">
         <f>IF(Q55&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S55" s="12">
+      <c r="S55" s="13">
         <f>H55*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>2.053461805</v>
       </c>
-      <c r="T55" s="13">
+      <c r="T55" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S55/(0.85*$B$2)))</f>
         <v>0.005120547802</v>
       </c>
-      <c r="U55" s="10">
+      <c r="U55" s="11">
         <f>T55*$H$2*1000*$Z$2</f>
         <v>233.228151</v>
       </c>
-      <c r="V55" s="10">
+      <c r="V55" s="11">
         <f>MAX(U55,$AB$2)</f>
         <v>233.228151</v>
       </c>
-      <c r="W55" s="14">
+      <c r="W55" s="15">
         <f>ROUNDUP(V55/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X55" s="15" t="str">
+      <c r="X55" s="16" t="str">
         <f>IF(J55&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y55" s="12">
+      <c r="Y55" s="13">
         <f>D55/IF(C55="1EC",18.5,IF(C55="2EC",21,8))</f>
         <v>0.2452380952</v>
       </c>
-      <c r="Z55" s="15" t="str">
+      <c r="Z55" s="16" t="str">
         <f>IF($J$2&gt;=Y55,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6325,105 +6439,105 @@
       <c r="B56" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D56" s="8" t="n">
+      <c r="D56" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F56" s="10">
+      <c r="F56" s="11">
         <f>IF(C56="1EC",10,IF(C56="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G56" s="10">
+      <c r="G56" s="11">
         <f>IF(C56="1EC",14,IF(C56="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H56" s="11">
+      <c r="H56" s="12">
         <f>E56*D56^2/F56</f>
         <v>4.250021236</v>
       </c>
-      <c r="I56" s="11">
+      <c r="I56" s="12">
         <f>IF(C56="V",0,E56*D56^2/G56)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J56" s="11">
+      <c r="J56" s="12">
         <f>IF(C56="V",E56*D56,IF(C56="1EC",1.15,1)*E56*D56/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K56" s="10">
+      <c r="K56" s="11">
         <f>MIN(D56*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L56" s="12">
+      <c r="L56" s="13">
         <f>I56*1000000/(0.9*K56*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M56" s="13">
+      <c r="M56" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L56/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N56" s="10">
+      <c r="N56" s="11">
         <f>M56*K56*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O56" s="10">
+      <c r="O56" s="11">
         <f>MAX(N56,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P56" s="14">
+      <c r="P56" s="15">
         <f>ROUNDUP(O56/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q56" s="11">
+      <c r="Q56" s="12">
         <f>O56*$D$2/(0.85*$B$2*K56)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R56" s="15" t="str">
+      <c r="R56" s="16" t="str">
         <f>IF(Q56&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S56" s="12">
+      <c r="S56" s="13">
         <f>H56*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T56" s="13">
+      <c r="T56" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S56/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U56" s="10">
+      <c r="U56" s="11">
         <f>T56*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V56" s="10">
+      <c r="V56" s="11">
         <f>MAX(U56,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W56" s="14">
+      <c r="W56" s="15">
         <f>ROUNDUP(V56/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X56" s="15" t="str">
+      <c r="X56" s="16" t="str">
         <f>IF(J56&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y56" s="12">
+      <c r="Y56" s="13">
         <f>D56/IF(C56="1EC",18.5,IF(C56="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z56" s="15" t="str">
+      <c r="Z56" s="16" t="str">
         <f>IF($J$2&gt;=Y56,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6431,105 +6545,105 @@
       <c r="B57" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D57" s="8" t="n">
+      <c r="D57" s="22" t="n">
         <v>3.6</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F57" s="10">
+      <c r="F57" s="11">
         <f>IF(C57="1EC",10,IF(C57="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G57" s="10">
+      <c r="G57" s="11">
         <f>IF(C57="1EC",14,IF(C57="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H57" s="11">
+      <c r="H57" s="12">
         <f>E57*D57^2/F57</f>
         <v>12.48985833</v>
       </c>
-      <c r="I57" s="11">
+      <c r="I57" s="12">
         <f>IF(C57="V",0,E57*D57^2/G57)</f>
         <v>8.5867776</v>
       </c>
-      <c r="J57" s="11">
+      <c r="J57" s="12">
         <f>IF(C57="V",E57*D57,IF(C57="1EC",1.15,1)*E57*D57/2)</f>
         <v>19.081728</v>
       </c>
-      <c r="K57" s="10">
+      <c r="K57" s="11">
         <f>MIN(D57*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L57" s="12">
+      <c r="L57" s="13">
         <f>I57*1000000/(0.9*K57*$Z$2^2)</f>
         <v>0.1293454474</v>
       </c>
-      <c r="M57" s="13">
+      <c r="M57" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L57/(0.85*$B$2)))</f>
         <v>0.000308806777</v>
       </c>
-      <c r="N57" s="10">
+      <c r="N57" s="11">
         <f>M57*K57*$Z$2</f>
         <v>75.01534228</v>
       </c>
-      <c r="O57" s="10">
+      <c r="O57" s="11">
         <f>MAX(N57,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P57" s="14">
+      <c r="P57" s="15">
         <f>ROUNDUP(O57/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q57" s="11">
+      <c r="Q57" s="12">
         <f>O57*$D$2/(0.85*$B$2*K57)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R57" s="15" t="str">
+      <c r="R57" s="16" t="str">
         <f>IF(Q57&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S57" s="12">
+      <c r="S57" s="13">
         <f>H57*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.003407107</v>
       </c>
-      <c r="T57" s="13">
+      <c r="T57" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S57/(0.85*$B$2)))</f>
         <v>0.002441668159</v>
       </c>
-      <c r="U57" s="10">
+      <c r="U57" s="11">
         <f>T57*$H$2*1000*$Z$2</f>
         <v>111.2118805</v>
       </c>
-      <c r="V57" s="10">
+      <c r="V57" s="11">
         <f>MAX(U57,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W57" s="14">
+      <c r="W57" s="15">
         <f>ROUNDUP(V57/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X57" s="15" t="str">
+      <c r="X57" s="16" t="str">
         <f>IF(J57&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y57" s="12">
+      <c r="Y57" s="13">
         <f>D57/IF(C57="1EC",18.5,IF(C57="2EC",21,8))</f>
         <v>0.1714285714</v>
       </c>
-      <c r="Z57" s="15" t="str">
+      <c r="Z57" s="16" t="str">
         <f>IF($J$2&gt;=Y57,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6537,105 +6651,105 @@
       <c r="B58" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D58" s="8" t="n">
+      <c r="D58" s="24" t="n">
         <v>5.1</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F58" s="11">
         <f>IF(C58="1EC",10,IF(C58="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G58" s="10">
+      <c r="G58" s="11">
         <f>IF(C58="1EC",14,IF(C58="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H58" s="11">
+      <c r="H58" s="12">
         <f>E58*D58^2/F58</f>
         <v>25.06645178</v>
       </c>
-      <c r="I58" s="11">
+      <c r="I58" s="12">
         <f>IF(C58="V",0,E58*D58^2/G58)</f>
         <v>17.2331856</v>
       </c>
-      <c r="J58" s="11">
+      <c r="J58" s="12">
         <f>IF(C58="V",E58*D58,IF(C58="1EC",1.15,1)*E58*D58/2)</f>
         <v>27.032448</v>
       </c>
-      <c r="K58" s="10">
+      <c r="K58" s="11">
         <f>MIN(D58*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L58" s="12">
+      <c r="L58" s="13">
         <f>I58*1000000/(0.9*K58*$Z$2^2)</f>
         <v>0.2595891271</v>
       </c>
-      <c r="M58" s="13">
+      <c r="M58" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L58/(0.85*$B$2)))</f>
         <v>0.0006214772975</v>
       </c>
-      <c r="N58" s="10">
+      <c r="N58" s="11">
         <f>M58*K58*$Z$2</f>
         <v>150.9692651</v>
       </c>
-      <c r="O58" s="10">
+      <c r="O58" s="11">
         <f>MAX(N58,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P58" s="14">
+      <c r="P58" s="15">
         <f>ROUNDUP(O58/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q58" s="11">
+      <c r="Q58" s="12">
         <f>O58*$D$2/(0.85*$B$2*K58)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R58" s="15" t="str">
+      <c r="R58" s="16" t="str">
         <f>IF(Q58&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S58" s="12">
+      <c r="S58" s="13">
         <f>H58*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>2.013782319</v>
       </c>
-      <c r="T58" s="13">
+      <c r="T58" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S58/(0.85*$B$2)))</f>
         <v>0.005016792195</v>
       </c>
-      <c r="U58" s="10">
+      <c r="U58" s="11">
         <f>T58*$H$2*1000*$Z$2</f>
         <v>228.5023425</v>
       </c>
-      <c r="V58" s="10">
+      <c r="V58" s="11">
         <f>MAX(U58,$AB$2)</f>
         <v>228.5023425</v>
       </c>
-      <c r="W58" s="14">
+      <c r="W58" s="15">
         <f>ROUNDUP(V58/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X58" s="15" t="str">
+      <c r="X58" s="16" t="str">
         <f>IF(J58&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y58" s="12">
+      <c r="Y58" s="13">
         <f>D58/IF(C58="1EC",18.5,IF(C58="2EC",21,8))</f>
         <v>0.2428571429</v>
       </c>
-      <c r="Z58" s="15" t="str">
+      <c r="Z58" s="16" t="str">
         <f>IF($J$2&gt;=Y58,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6643,105 +6757,105 @@
       <c r="B59" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D59" s="8" t="n">
+      <c r="D59" s="22" t="n">
         <v>3.6</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F59" s="11">
         <f>IF(C59="1EC",10,IF(C59="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G59" s="10">
+      <c r="G59" s="11">
         <f>IF(C59="1EC",14,IF(C59="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H59" s="11">
+      <c r="H59" s="12">
         <f>E59*D59^2/F59</f>
         <v>12.48985833</v>
       </c>
-      <c r="I59" s="11">
+      <c r="I59" s="12">
         <f>IF(C59="V",0,E59*D59^2/G59)</f>
         <v>8.5867776</v>
       </c>
-      <c r="J59" s="11">
+      <c r="J59" s="12">
         <f>IF(C59="V",E59*D59,IF(C59="1EC",1.15,1)*E59*D59/2)</f>
         <v>19.081728</v>
       </c>
-      <c r="K59" s="10">
+      <c r="K59" s="11">
         <f>MIN(D59*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L59" s="12">
+      <c r="L59" s="13">
         <f>I59*1000000/(0.9*K59*$Z$2^2)</f>
         <v>0.1293454474</v>
       </c>
-      <c r="M59" s="13">
+      <c r="M59" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L59/(0.85*$B$2)))</f>
         <v>0.000308806777</v>
       </c>
-      <c r="N59" s="10">
+      <c r="N59" s="11">
         <f>M59*K59*$Z$2</f>
         <v>75.01534228</v>
       </c>
-      <c r="O59" s="10">
+      <c r="O59" s="11">
         <f>MAX(N59,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P59" s="14">
+      <c r="P59" s="15">
         <f>ROUNDUP(O59/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q59" s="11">
+      <c r="Q59" s="12">
         <f>O59*$D$2/(0.85*$B$2*K59)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R59" s="15" t="str">
+      <c r="R59" s="16" t="str">
         <f>IF(Q59&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S59" s="12">
+      <c r="S59" s="13">
         <f>H59*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.003407107</v>
       </c>
-      <c r="T59" s="13">
+      <c r="T59" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S59/(0.85*$B$2)))</f>
         <v>0.002441668159</v>
       </c>
-      <c r="U59" s="10">
+      <c r="U59" s="11">
         <f>T59*$H$2*1000*$Z$2</f>
         <v>111.2118805</v>
       </c>
-      <c r="V59" s="10">
+      <c r="V59" s="11">
         <f>MAX(U59,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W59" s="14">
+      <c r="W59" s="15">
         <f>ROUNDUP(V59/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X59" s="15" t="str">
+      <c r="X59" s="16" t="str">
         <f>IF(J59&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y59" s="12">
+      <c r="Y59" s="13">
         <f>D59/IF(C59="1EC",18.5,IF(C59="2EC",21,8))</f>
         <v>0.1714285714</v>
       </c>
-      <c r="Z59" s="15" t="str">
+      <c r="Z59" s="16" t="str">
         <f>IF($J$2&gt;=Y59,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6749,105 +6863,105 @@
       <c r="B60" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D60" s="8" t="n">
+      <c r="D60" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F60" s="10">
+      <c r="F60" s="11">
         <f>IF(C60="1EC",10,IF(C60="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G60" s="10">
+      <c r="G60" s="11">
         <f>IF(C60="1EC",14,IF(C60="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H60" s="11">
+      <c r="H60" s="12">
         <f>E60*D60^2/F60</f>
         <v>4.250021236</v>
       </c>
-      <c r="I60" s="11">
+      <c r="I60" s="12">
         <f>IF(C60="V",0,E60*D60^2/G60)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J60" s="11">
+      <c r="J60" s="12">
         <f>IF(C60="V",E60*D60,IF(C60="1EC",1.15,1)*E60*D60/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K60" s="10">
+      <c r="K60" s="11">
         <f>MIN(D60*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L60" s="12">
+      <c r="L60" s="13">
         <f>I60*1000000/(0.9*K60*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M60" s="13">
+      <c r="M60" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L60/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N60" s="10">
+      <c r="N60" s="11">
         <f>M60*K60*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O60" s="10">
+      <c r="O60" s="11">
         <f>MAX(N60,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P60" s="14">
+      <c r="P60" s="15">
         <f>ROUNDUP(O60/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q60" s="11">
+      <c r="Q60" s="12">
         <f>O60*$D$2/(0.85*$B$2*K60)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R60" s="15" t="str">
+      <c r="R60" s="16" t="str">
         <f>IF(Q60&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S60" s="12">
+      <c r="S60" s="13">
         <f>H60*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T60" s="13">
+      <c r="T60" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S60/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U60" s="10">
+      <c r="U60" s="11">
         <f>T60*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V60" s="10">
+      <c r="V60" s="11">
         <f>MAX(U60,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W60" s="14">
+      <c r="W60" s="15">
         <f>ROUNDUP(V60/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X60" s="15" t="str">
+      <c r="X60" s="16" t="str">
         <f>IF(J60&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y60" s="12">
+      <c r="Y60" s="13">
         <f>D60/IF(C60="1EC",18.5,IF(C60="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z60" s="15" t="str">
+      <c r="Z60" s="16" t="str">
         <f>IF($J$2&gt;=Y60,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6855,105 +6969,105 @@
       <c r="B61" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n">
+      <c r="D61" s="28" t="n">
         <v>3.8</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F61" s="10">
+      <c r="F61" s="11">
         <f>IF(C61="1EC",10,IF(C61="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G61" s="10">
+      <c r="G61" s="11">
         <f>IF(C61="1EC",14,IF(C61="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H61" s="11">
+      <c r="H61" s="12">
         <f>E61*D61^2/F61</f>
         <v>13.91616931</v>
       </c>
-      <c r="I61" s="11">
+      <c r="I61" s="12">
         <f>IF(C61="V",0,E61*D61^2/G61)</f>
         <v>9.5673664</v>
       </c>
-      <c r="J61" s="11">
+      <c r="J61" s="12">
         <f>IF(C61="V",E61*D61,IF(C61="1EC",1.15,1)*E61*D61/2)</f>
         <v>20.141824</v>
       </c>
-      <c r="K61" s="10">
+      <c r="K61" s="11">
         <f>MIN(D61*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L61" s="12">
+      <c r="L61" s="13">
         <f>I61*1000000/(0.9*K61*$Z$2^2)</f>
         <v>0.1441163781</v>
       </c>
-      <c r="M61" s="13">
+      <c r="M61" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L61/(0.85*$B$2)))</f>
         <v>0.0003441794645</v>
       </c>
-      <c r="N61" s="10">
+      <c r="N61" s="11">
         <f>M61*K61*$Z$2</f>
         <v>83.60807552</v>
       </c>
-      <c r="O61" s="10">
+      <c r="O61" s="11">
         <f>MAX(N61,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P61" s="14">
+      <c r="P61" s="15">
         <f>ROUNDUP(O61/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q61" s="11">
+      <c r="Q61" s="12">
         <f>O61*$D$2/(0.85*$B$2*K61)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R61" s="15" t="str">
+      <c r="R61" s="16" t="str">
         <f>IF(Q61&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S61" s="12">
+      <c r="S61" s="13">
         <f>H61*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.117993721</v>
       </c>
-      <c r="T61" s="13">
+      <c r="T61" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S61/(0.85*$B$2)))</f>
         <v>0.002727531841</v>
       </c>
-      <c r="U61" s="10">
+      <c r="U61" s="11">
         <f>T61*$H$2*1000*$Z$2</f>
         <v>124.2322565</v>
       </c>
-      <c r="V61" s="10">
+      <c r="V61" s="11">
         <f>MAX(U61,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W61" s="14">
+      <c r="W61" s="15">
         <f>ROUNDUP(V61/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X61" s="15" t="str">
+      <c r="X61" s="16" t="str">
         <f>IF(J61&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y61" s="12">
+      <c r="Y61" s="13">
         <f>D61/IF(C61="1EC",18.5,IF(C61="2EC",21,8))</f>
         <v>0.180952381</v>
       </c>
-      <c r="Z61" s="15" t="str">
+      <c r="Z61" s="16" t="str">
         <f>IF($J$2&gt;=Y61,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -6961,105 +7075,105 @@
       <c r="B62" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D62" s="8" t="n">
+      <c r="D62" s="20" t="n">
         <v>2.1</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F62" s="10">
+      <c r="F62" s="11">
         <f>IF(C62="1EC",10,IF(C62="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G62" s="10">
+      <c r="G62" s="11">
         <f>IF(C62="1EC",14,IF(C62="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H62" s="11">
+      <c r="H62" s="12">
         <f>E62*D62^2/F62</f>
         <v>4.250021236</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I62" s="12">
         <f>IF(C62="V",0,E62*D62^2/G62)</f>
         <v>2.9218896</v>
       </c>
-      <c r="J62" s="11">
+      <c r="J62" s="12">
         <f>IF(C62="V",E62*D62,IF(C62="1EC",1.15,1)*E62*D62/2)</f>
         <v>11.131008</v>
       </c>
-      <c r="K62" s="10">
+      <c r="K62" s="11">
         <f>MIN(D62*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>525</v>
       </c>
-      <c r="L62" s="12">
+      <c r="L62" s="13">
         <f>I62*1000000/(0.9*K62*$Z$2^2)</f>
         <v>0.06706800976</v>
       </c>
-      <c r="M62" s="13">
+      <c r="M62" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L62/(0.85*$B$2)))</f>
         <v>0.0001599113697</v>
       </c>
-      <c r="N62" s="10">
+      <c r="N62" s="11">
         <f>M62*K62*$Z$2</f>
         <v>25.49247089</v>
       </c>
-      <c r="O62" s="10">
+      <c r="O62" s="11">
         <f>MAX(N62,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P62" s="14">
+      <c r="P62" s="15">
         <f>ROUNDUP(O62/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q62" s="11">
+      <c r="Q62" s="12">
         <f>O62*$D$2/(0.85*$B$2*K62)</f>
         <v>5.103361345</v>
       </c>
-      <c r="R62" s="15" t="str">
+      <c r="R62" s="16" t="str">
         <f>IF(Q62&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S62" s="12">
+      <c r="S62" s="13">
         <f>H62*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.3414371406</v>
       </c>
-      <c r="T62" s="13">
+      <c r="T62" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S62/(0.85*$B$2)))</f>
         <v>0.0008188620588</v>
       </c>
-      <c r="U62" s="10">
+      <c r="U62" s="11">
         <f>T62*$H$2*1000*$Z$2</f>
         <v>37.29711962</v>
       </c>
-      <c r="V62" s="10">
+      <c r="V62" s="11">
         <f>MAX(U62,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W62" s="14">
+      <c r="W62" s="15">
         <f>ROUNDUP(V62/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X62" s="15" t="str">
+      <c r="X62" s="16" t="str">
         <f>IF(J62&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y62" s="12">
+      <c r="Y62" s="13">
         <f>D62/IF(C62="1EC",18.5,IF(C62="2EC",21,8))</f>
         <v>0.1</v>
       </c>
-      <c r="Z62" s="15" t="str">
+      <c r="Z62" s="16" t="str">
         <f>IF($J$2&gt;=Y62,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" s="35" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -7067,105 +7181,105 @@
       <c r="B63" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D63" s="8" t="n">
+      <c r="D63" s="36" t="n">
         <v>5.15</v>
       </c>
-      <c r="E63" s="9">
+      <c r="E63" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F63" s="10">
+      <c r="F63" s="11">
         <f>IF(C63="1EC",10,IF(C63="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G63" s="10">
+      <c r="G63" s="11">
         <f>IF(C63="1EC",14,IF(C63="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H63" s="12">
         <f>E63*D63^2/F63</f>
         <v>25.56036015</v>
       </c>
-      <c r="I63" s="11">
+      <c r="I63" s="12">
         <f>IF(C63="V",0,E63*D63^2/G63)</f>
         <v>17.5727476</v>
       </c>
-      <c r="J63" s="11">
+      <c r="J63" s="12">
         <f>IF(C63="V",E63*D63,IF(C63="1EC",1.15,1)*E63*D63/2)</f>
         <v>27.297472</v>
       </c>
-      <c r="K63" s="10">
+      <c r="K63" s="11">
         <f>MIN(D63*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L63" s="12">
+      <c r="L63" s="13">
         <f>I63*1000000/(0.9*K63*$Z$2^2)</f>
         <v>0.2647040608</v>
       </c>
-      <c r="M63" s="13">
+      <c r="M63" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L63/(0.85*$B$2)))</f>
         <v>0.0006337921089</v>
       </c>
-      <c r="N63" s="10">
+      <c r="N63" s="11">
         <f>M63*K63*$Z$2</f>
         <v>153.9607791</v>
       </c>
-      <c r="O63" s="10">
+      <c r="O63" s="11">
         <f>MAX(N63,$AB$2)</f>
         <v>153.9607791</v>
       </c>
-      <c r="P63" s="14">
+      <c r="P63" s="15">
         <f>ROUNDUP(O63/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q63" s="11">
+      <c r="Q63" s="12">
         <f>O63*$D$2/(0.85*$B$2*K63)</f>
         <v>3.396193657</v>
       </c>
-      <c r="R63" s="15" t="str">
+      <c r="R63" s="16" t="str">
         <f>IF(Q63&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S63" s="12">
+      <c r="S63" s="13">
         <f>H63*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>2.053461805</v>
       </c>
-      <c r="T63" s="13">
+      <c r="T63" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S63/(0.85*$B$2)))</f>
         <v>0.005120547802</v>
       </c>
-      <c r="U63" s="10">
+      <c r="U63" s="11">
         <f>T63*$H$2*1000*$Z$2</f>
         <v>233.228151</v>
       </c>
-      <c r="V63" s="10">
+      <c r="V63" s="11">
         <f>MAX(U63,$AB$2)</f>
         <v>233.228151</v>
       </c>
-      <c r="W63" s="14">
+      <c r="W63" s="15">
         <f>ROUNDUP(V63/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X63" s="15" t="str">
+      <c r="X63" s="16" t="str">
         <f>IF(J63&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y63" s="12">
+      <c r="Y63" s="13">
         <f>D63/IF(C63="1EC",18.5,IF(C63="2EC",21,8))</f>
         <v>0.2452380952</v>
       </c>
-      <c r="Z63" s="15" t="str">
+      <c r="Z63" s="16" t="str">
         <f>IF($J$2&gt;=Y63,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" s="33" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -7173,105 +7287,105 @@
       <c r="B64" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>2EC</t>
         </is>
       </c>
-      <c r="D64" s="8" t="n">
+      <c r="D64" s="34" t="n">
         <v>4.8</v>
       </c>
-      <c r="E64" s="9">
+      <c r="E64" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F64" s="10">
+      <c r="F64" s="11">
         <f>IF(C64="1EC",10,IF(C64="2EC",11,2))</f>
         <v>11</v>
       </c>
-      <c r="G64" s="10">
+      <c r="G64" s="11">
         <f>IF(C64="1EC",14,IF(C64="2EC",16,0))</f>
         <v>16</v>
       </c>
-      <c r="H64" s="11">
+      <c r="H64" s="12">
         <f>E64*D64^2/F64</f>
         <v>22.20419258</v>
       </c>
-      <c r="I64" s="11">
+      <c r="I64" s="12">
         <f>IF(C64="V",0,E64*D64^2/G64)</f>
         <v>15.2653824</v>
       </c>
-      <c r="J64" s="11">
+      <c r="J64" s="12">
         <f>IF(C64="V",E64*D64,IF(C64="1EC",1.15,1)*E64*D64/2)</f>
         <v>25.442304</v>
       </c>
-      <c r="K64" s="10">
+      <c r="K64" s="11">
         <f>MIN(D64*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>800</v>
       </c>
-      <c r="L64" s="12">
+      <c r="L64" s="13">
         <f>I64*1000000/(0.9*K64*$Z$2^2)</f>
         <v>0.229947462</v>
       </c>
-      <c r="M64" s="13">
+      <c r="M64" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L64/(0.85*$B$2)))</f>
         <v>0.0005501646734</v>
       </c>
-      <c r="N64" s="10">
+      <c r="N64" s="11">
         <f>M64*K64*$Z$2</f>
         <v>133.6460025</v>
       </c>
-      <c r="O64" s="10">
+      <c r="O64" s="11">
         <f>MAX(N64,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P64" s="14">
+      <c r="P64" s="15">
         <f>ROUNDUP(O64/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q64" s="11">
+      <c r="Q64" s="12">
         <f>O64*$D$2/(0.85*$B$2*K64)</f>
         <v>3.349080882</v>
       </c>
-      <c r="R64" s="15" t="str">
+      <c r="R64" s="16" t="str">
         <f>IF(Q64&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S64" s="12">
+      <c r="S64" s="13">
         <f>H64*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>1.783834857</v>
       </c>
-      <c r="T64" s="13">
+      <c r="T64" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S64/(0.85*$B$2)))</f>
         <v>0.004419572507</v>
       </c>
-      <c r="U64" s="10">
+      <c r="U64" s="11">
         <f>T64*$H$2*1000*$Z$2</f>
         <v>201.3004788</v>
       </c>
-      <c r="V64" s="10">
+      <c r="V64" s="11">
         <f>MAX(U64,$AB$2)</f>
         <v>201.3004788</v>
       </c>
-      <c r="W64" s="14">
+      <c r="W64" s="15">
         <f>ROUNDUP(V64/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X64" s="15" t="str">
+      <c r="X64" s="16" t="str">
         <f>IF(J64&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y64" s="12">
+      <c r="Y64" s="13">
         <f>D64/IF(C64="1EC",18.5,IF(C64="2EC",21,8))</f>
         <v>0.2285714286</v>
       </c>
-      <c r="Z64" s="15" t="str">
+      <c r="Z64" s="16" t="str">
         <f>IF($J$2&gt;=Y64,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>VIGUETA 6</t>
         </is>
@@ -7279,108 +7393,150 @@
       <c r="B65" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D65" s="8" t="n">
+      <c r="D65" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="E65" s="9">
+      <c r="E65" s="10">
         <f>$X$2</f>
         <v>10.60096</v>
       </c>
-      <c r="F65" s="10">
+      <c r="F65" s="11">
         <f>IF(C65="1EC",10,IF(C65="2EC",11,2))</f>
         <v>2</v>
       </c>
-      <c r="G65" s="10">
+      <c r="G65" s="11">
         <f>IF(C65="1EC",14,IF(C65="2EC",16,0))</f>
         <v>0</v>
       </c>
-      <c r="H65" s="11">
+      <c r="H65" s="12">
         <f>E65*D65^2/F65</f>
         <v>11.92608</v>
       </c>
-      <c r="I65" s="11">
+      <c r="I65" s="12">
         <f>IF(C65="V",0,E65*D65^2/G65)</f>
         <v>0</v>
       </c>
-      <c r="J65" s="11">
+      <c r="J65" s="12">
         <f>IF(C65="V",E65*D65,IF(C65="1EC",1.15,1)*E65*D65/2)</f>
         <v>15.90144</v>
       </c>
-      <c r="K65" s="10">
+      <c r="K65" s="11">
         <f>MIN(D65*1000/4,$H$2*1000+16*$L$2*1000,$N$2*1000)</f>
         <v>375</v>
       </c>
-      <c r="L65" s="12">
+      <c r="L65" s="13">
         <f>I65*1000000/(0.9*K65*$Z$2^2)</f>
         <v>0</v>
       </c>
-      <c r="M65" s="13">
+      <c r="M65" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*L65/(0.85*$B$2)))</f>
         <v>0</v>
       </c>
-      <c r="N65" s="10">
+      <c r="N65" s="11">
         <f>M65*K65*$Z$2</f>
         <v>0</v>
       </c>
-      <c r="O65" s="10">
+      <c r="O65" s="11">
         <f>MAX(N65,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="P65" s="14">
+      <c r="P65" s="15">
         <f>ROUNDUP(O65/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="Q65" s="11">
+      <c r="Q65" s="12">
         <f>O65*$D$2/(0.85*$B$2*K65)</f>
         <v>7.144705882</v>
       </c>
-      <c r="R65" s="15" t="str">
+      <c r="R65" s="16" t="str">
         <f>IF(Q65&lt;=$L$2*1000,"Si (T)","revisar")</f>
         <v>Si (T)</v>
       </c>
-      <c r="S65" s="12">
+      <c r="S65" s="13">
         <f>H65*1000000/(0.9*$H$2*1000*$Z$2^2)</f>
         <v>0.9581144251</v>
       </c>
-      <c r="T65" s="13">
+      <c r="T65" s="14">
         <f>(0.85*$B$2/$D$2)*(1-SQRT(1-2*S65/(0.85*$B$2)))</f>
         <v>0.002329089448</v>
       </c>
-      <c r="U65" s="10">
+      <c r="U65" s="11">
         <f>T65*$H$2*1000*$Z$2</f>
         <v>106.0842016</v>
       </c>
-      <c r="V65" s="10">
+      <c r="V65" s="11">
         <f>MAX(U65,$AB$2)</f>
         <v>151.825</v>
       </c>
-      <c r="W65" s="14">
+      <c r="W65" s="15">
         <f>ROUNDUP(V65/$T$2,0)</f>
         <v>2</v>
       </c>
-      <c r="X65" s="15" t="str">
+      <c r="X65" s="16" t="str">
         <f>IF(J65&lt;=$AD$2,"No requiere","Requiere")</f>
         <v>No requiere</v>
       </c>
-      <c r="Y65" s="12">
+      <c r="Y65" s="13">
         <f>D65/IF(C65="1EC",18.5,IF(C65="2EC",21,8))</f>
         <v>0.1875</v>
       </c>
-      <c r="Z65" s="15" t="str">
+      <c r="Z65" s="16" t="str">
         <f>IF($J$2&gt;=Y65,"CUMPLE","REVISAR")</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>Resultado: los 62 vanos requieren solo 2 Nº4 inf + 2 Nº4 sup y no requieren estribos (Vu &lt;= phi 1.1 Vc = 33.8 kN). Carga = cubierta (gobierna). La loseta lleva malla de retraccion y temperatura.</t>
         </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="38" t="inlineStr">
+        <is>
+          <t>Leyenda de colores (mismo color = misma luz/grupo):</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B70" s="20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E70" s="30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G70" s="22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H70" s="28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I70" s="34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J70" s="24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K70" s="36" t="n">
+        <v>5.15</v>
       </c>
     </row>
   </sheetData>
